--- a/data/TTN/最新版班表/2026-10/TTN_TD.xlsx
+++ b/data/TTN/最新版班表/2026-10/TTN_TD.xlsx
@@ -882,16 +882,17 @@
 8:00</t>
         </is>
       </c>
-      <c r="D7" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="E7" s="1" t="inlineStr">
+        <is>
+          <t>4:42
+ND0014
+12:42
+8:00</t>
         </is>
       </c>
       <c r="F7" s="1" t="inlineStr">
@@ -910,25 +911,19 @@
 8:16</t>
         </is>
       </c>
-      <c r="H7" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
-        </is>
-      </c>
-      <c r="I7" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO2
-</t>
-        </is>
-      </c>
-      <c r="J7" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>DO2</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="K7" s="1" t="inlineStr">
@@ -963,11 +958,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="O7" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="P7" s="1" t="inlineStr">
@@ -994,18 +987,14 @@
 8:38</t>
         </is>
       </c>
-      <c r="S7" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="T7" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="U7" s="1" t="inlineStr">
@@ -1049,18 +1038,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="Z7" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="AA7" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="AB7" s="1" t="inlineStr">
@@ -1099,11 +1084,9 @@
           <t>林行憲</t>
         </is>
       </c>
-      <c r="C8" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="D8" s="1" t="inlineStr">
@@ -1116,25 +1099,23 @@
       </c>
       <c r="E8" s="1" t="inlineStr">
         <is>
-          <t>8:30
-NGRSD
-17:30
-9:00</t>
-        </is>
-      </c>
-      <c r="F8" s="1" t="inlineStr">
-        <is>
           <t>21:00
 NGRSN
 30:00
 9:00</t>
         </is>
       </c>
-      <c r="G8" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="F8" s="1" t="inlineStr">
+        <is>
+          <t>21:00
+NGRSN
+30:00
+9:00</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="H8" s="1" t="inlineStr">
@@ -1145,18 +1126,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="I8" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO2
-</t>
-        </is>
-      </c>
-      <c r="J8" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>DO2</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="K8" s="1" t="inlineStr">
@@ -1208,11 +1185,9 @@
 9:00</t>
         </is>
       </c>
-      <c r="Q8" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="R8" s="1" t="inlineStr">
@@ -1255,18 +1230,14 @@
 9:00</t>
         </is>
       </c>
-      <c r="W8" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
-        </is>
-      </c>
-      <c r="X8" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO2
-</t>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>DO2</t>
         </is>
       </c>
       <c r="Y8" s="1" t="inlineStr">
@@ -1310,11 +1281,9 @@
 9:00</t>
         </is>
       </c>
-      <c r="AD8" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
     </row>
@@ -1337,18 +1306,16 @@
 9:26</t>
         </is>
       </c>
-      <c r="D9" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="E9" s="1" t="inlineStr">
         <is>
-          <t>14:13
-ND0564
-22:13
+          <t>8:30
+TTN
+17:30
 8:00</t>
         </is>
       </c>
@@ -1368,11 +1335,9 @@
 8:11</t>
         </is>
       </c>
-      <c r="H9" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="I9" s="1" t="inlineStr">
@@ -1408,18 +1373,14 @@
 9:20</t>
         </is>
       </c>
-      <c r="M9" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="N9" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="O9" s="1" t="inlineStr">
@@ -1454,11 +1415,9 @@
 9:51</t>
         </is>
       </c>
-      <c r="S9" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="T9" s="1" t="inlineStr">
@@ -1477,11 +1436,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="V9" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="W9" s="1" t="inlineStr">
@@ -1525,18 +1482,14 @@
 9:51</t>
         </is>
       </c>
-      <c r="AB9" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="AC9" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="AD9" s="1" t="inlineStr">
@@ -1559,23 +1512,22 @@
           <t>李國維</t>
         </is>
       </c>
-      <c r="C10" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="E10" s="1" t="inlineStr">
+        <is>
+          <t>6:00
+STD2
+14:00
+8:00</t>
         </is>
       </c>
       <c r="F10" s="1" t="inlineStr">
@@ -1602,18 +1554,14 @@
 9:26</t>
         </is>
       </c>
-      <c r="I10" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO2
-</t>
-        </is>
-      </c>
-      <c r="J10" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>DO2</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="K10" s="1" t="inlineStr">
@@ -1648,11 +1596,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="O10" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="P10" s="1" t="inlineStr">
@@ -1687,25 +1633,19 @@
 8:00</t>
         </is>
       </c>
-      <c r="T10" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO2
-</t>
-        </is>
-      </c>
-      <c r="U10" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="V10" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>DO2</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="W10" s="1" t="inlineStr">
@@ -1741,18 +1681,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="AA10" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="AB10" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="AC10" s="1" t="inlineStr">
@@ -1791,16 +1727,17 @@
 8:00</t>
         </is>
       </c>
-      <c r="D11" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="E11" s="1" t="inlineStr">
+        <is>
+          <t>13:42
+ND0516
+23:03
+9:21</t>
         </is>
       </c>
       <c r="F11" s="1" t="inlineStr">
@@ -1811,11 +1748,9 @@
 8:41</t>
         </is>
       </c>
-      <c r="G11" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="H11" s="1" t="inlineStr">
@@ -1851,18 +1786,14 @@
 9:51</t>
         </is>
       </c>
-      <c r="L11" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="M11" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="N11" s="1" t="inlineStr">
@@ -1889,11 +1820,9 @@
 8:21</t>
         </is>
       </c>
-      <c r="Q11" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="R11" s="1" t="inlineStr">
@@ -1928,11 +1857,9 @@
 8:51</t>
         </is>
       </c>
-      <c r="V11" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="W11" s="1" t="inlineStr">
@@ -1968,18 +1895,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="AA11" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="AB11" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="AC11" s="1" t="inlineStr">
@@ -2028,179 +1951,159 @@
       </c>
       <c r="E12" s="1" t="inlineStr">
         <is>
+          <t>12:30
+STD4
+20:30
+8:00</t>
+        </is>
+      </c>
+      <c r="F12" s="1" t="inlineStr">
+        <is>
+          <t>12:30
+STD4
+20:30
+8:00</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>DO2</t>
+        </is>
+      </c>
+      <c r="J12" s="1" t="inlineStr">
+        <is>
+          <t>13:13
+ND5901
+21:13
+8:00</t>
+        </is>
+      </c>
+      <c r="K12" s="1" t="inlineStr">
+        <is>
+          <t>12:33
+ND0503
+20:33
+8:00</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="N12" s="1" t="inlineStr">
+        <is>
+          <t>8:30
+OGT3
+17:30
+8:00</t>
+        </is>
+      </c>
+      <c r="O12" s="1" t="inlineStr">
+        <is>
+          <t>13:02
+ND0578
+21:08
+8:06</t>
+        </is>
+      </c>
+      <c r="P12" s="1" t="inlineStr">
+        <is>
+          <t>12:13
+ND0501
+20:13
+8:00</t>
+        </is>
+      </c>
+      <c r="Q12" s="1" t="inlineStr">
+        <is>
+          <t>13:18
+ND0580
+21:18
+8:00</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>DO2</t>
+        </is>
+      </c>
+      <c r="U12" s="1" t="inlineStr">
+        <is>
+          <t>11:30
+STD3
+19:30
+8:00</t>
+        </is>
+      </c>
+      <c r="V12" s="1" t="inlineStr">
+        <is>
+          <t>13:13
+ND0513
+21:13
+8:00</t>
+        </is>
+      </c>
+      <c r="W12" s="1" t="inlineStr">
+        <is>
+          <t>11:30
+STD3
+19:30
+8:00</t>
+        </is>
+      </c>
+      <c r="X12" s="1" t="inlineStr">
+        <is>
+          <t>11:30
+DO2W
+STD3
+19:30
+8:00</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="AA12" s="1" t="inlineStr">
+        <is>
           <t>12:32
 ND0502
 21:13
 8:41</t>
         </is>
       </c>
-      <c r="F12" s="1" t="inlineStr">
-        <is>
-          <t>12:30
-STD4
-20:30
-8:00</t>
-        </is>
-      </c>
-      <c r="G12" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="H12" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
-        </is>
-      </c>
-      <c r="I12" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO2
-</t>
-        </is>
-      </c>
-      <c r="J12" s="1" t="inlineStr">
-        <is>
-          <t>13:13
-ND5901
-21:13
-8:00</t>
-        </is>
-      </c>
-      <c r="K12" s="1" t="inlineStr">
-        <is>
-          <t>12:33
-ND0503
-20:33
-8:00</t>
-        </is>
-      </c>
-      <c r="L12" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="M12" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
-        </is>
-      </c>
-      <c r="N12" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-OGT3
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="O12" s="1" t="inlineStr">
-        <is>
-          <t>13:02
-ND0578
-21:08
-8:06</t>
-        </is>
-      </c>
-      <c r="P12" s="1" t="inlineStr">
-        <is>
-          <t>12:13
-ND0501
-20:13
-8:00</t>
-        </is>
-      </c>
-      <c r="Q12" s="1" t="inlineStr">
-        <is>
-          <t>13:18
-ND0580
-21:18
-8:00</t>
-        </is>
-      </c>
-      <c r="R12" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="S12" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
-        </is>
-      </c>
-      <c r="T12" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO2
-</t>
-        </is>
-      </c>
-      <c r="U12" s="1" t="inlineStr">
-        <is>
-          <t>11:30
-STD3
-19:30
-8:00</t>
-        </is>
-      </c>
-      <c r="V12" s="1" t="inlineStr">
-        <is>
-          <t>13:13
-ND0513
-21:13
-8:00</t>
-        </is>
-      </c>
-      <c r="W12" s="1" t="inlineStr">
-        <is>
-          <t>11:30
-STD3
-19:30
-8:00</t>
-        </is>
-      </c>
-      <c r="X12" s="1" t="inlineStr">
-        <is>
-          <t>11:30
-DO2W
-STD3
-19:30
-8:00</t>
-        </is>
-      </c>
-      <c r="Y12" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="Z12" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
-        </is>
-      </c>
-      <c r="AA12" s="1" t="inlineStr">
-        <is>
-          <t>12:32
-ND0502
-21:13
-8:41</t>
-        </is>
-      </c>
       <c r="AB12" s="1" t="inlineStr">
         <is>
           <t>13:33
@@ -2237,11 +2140,9 @@
           <t>程耀輝</t>
         </is>
       </c>
-      <c r="C13" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="D13" s="1" t="inlineStr">
@@ -2254,10 +2155,10 @@
       </c>
       <c r="E13" s="1" t="inlineStr">
         <is>
-          <t>16:22
-ND0588
-24:38
-8:16</t>
+          <t>11:17
+ND0073
+19:17
+8:00</t>
         </is>
       </c>
       <c r="F13" s="1" t="inlineStr">
@@ -2276,18 +2177,14 @@
 8:06</t>
         </is>
       </c>
-      <c r="H13" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
-        </is>
-      </c>
-      <c r="I13" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO2
-</t>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>DO2</t>
         </is>
       </c>
       <c r="J13" s="1" t="inlineStr">
@@ -2330,18 +2227,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="O13" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="P13" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="Q13" s="1" t="inlineStr">
@@ -2352,18 +2245,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="R13" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="S13" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="T13" s="1" t="inlineStr">
@@ -2407,18 +2296,14 @@
 9:01</t>
         </is>
       </c>
-      <c r="Y13" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="Z13" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="AA13" s="1" t="inlineStr">
@@ -2473,14 +2358,25 @@
 8:00</t>
         </is>
       </c>
-      <c r="D14" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="E14" s="1" t="inlineStr">
+        <is>
+          <t>11:30
+STD3
+19:30
+8:00</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="G14" s="1" t="inlineStr">
         <is>
           <t>12:30
 STD4
@@ -2488,21 +2384,6 @@
 8:00</t>
         </is>
       </c>
-      <c r="F14" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
-        </is>
-      </c>
-      <c r="G14" s="1" t="inlineStr">
-        <is>
-          <t>12:30
-STD4
-20:30
-8:00</t>
-        </is>
-      </c>
       <c r="H14" s="1" t="inlineStr">
         <is>
           <t>8:30
@@ -2511,11 +2392,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="I14" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO2
-</t>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>DO2</t>
         </is>
       </c>
       <c r="J14" s="1" t="inlineStr">
@@ -2526,11 +2405,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="K14" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="L14" s="1" t="inlineStr">
@@ -2565,11 +2442,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="P14" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="Q14" s="1" t="inlineStr">
@@ -2596,18 +2471,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="T14" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="U14" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="V14" s="1" t="inlineStr">
@@ -2643,11 +2514,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="Z14" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="AA14" s="1" t="inlineStr">
@@ -2674,11 +2543,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="AD14" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
     </row>
@@ -2886,19 +2753,17 @@
 8:00</t>
         </is>
       </c>
-      <c r="D16" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="E16" s="1" t="inlineStr">
         <is>
-          <t>6:22
-ND0007
-14:22
-8:00</t>
+          <t>16:22
+FAC1
+24:38
+8:16</t>
         </is>
       </c>
       <c r="F16" s="1" t="inlineStr">
@@ -2917,18 +2782,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="H16" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
-        </is>
-      </c>
-      <c r="I16" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO2
-</t>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>DO2</t>
         </is>
       </c>
       <c r="J16" s="1" t="inlineStr">
@@ -2963,18 +2824,14 @@
 9:38</t>
         </is>
       </c>
-      <c r="N16" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="O16" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="P16" s="1" t="inlineStr">
@@ -3017,18 +2874,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="U16" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="V16" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="W16" s="1" t="inlineStr">
@@ -3080,18 +2933,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="AC16" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="AD16" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
     </row>
@@ -3106,11 +2955,9 @@
           <t>袁皓威</t>
         </is>
       </c>
-      <c r="C17" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="D17" s="1" t="inlineStr">
@@ -3145,25 +2992,19 @@
 8:00</t>
         </is>
       </c>
-      <c r="H17" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
-        </is>
-      </c>
-      <c r="I17" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO2
-</t>
-        </is>
-      </c>
-      <c r="J17" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>DO2</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="K17" s="1" t="inlineStr">
@@ -3206,18 +3047,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="P17" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
-        </is>
-      </c>
-      <c r="Q17" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="R17" s="1" t="inlineStr">
@@ -3260,25 +3097,19 @@
 8:00</t>
         </is>
       </c>
-      <c r="W17" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
-        </is>
-      </c>
-      <c r="X17" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO2
-</t>
-        </is>
-      </c>
-      <c r="Y17" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>DO2</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="Z17" s="1" t="inlineStr">
@@ -3313,11 +3144,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="AD17" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
     </row>
@@ -3340,16 +3169,17 @@
 8:00</t>
         </is>
       </c>
-      <c r="D18" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="E18" s="1" t="inlineStr">
+        <is>
+          <t>7:12
+ND0088
+16:13
+9:01</t>
         </is>
       </c>
       <c r="F18" s="1" t="inlineStr">
@@ -3360,39 +3190,29 @@
 9:00</t>
         </is>
       </c>
-      <c r="G18" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO2
-</t>
-        </is>
-      </c>
-      <c r="H18" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
-        </is>
-      </c>
-      <c r="I18" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO2
-</t>
-        </is>
-      </c>
-      <c r="J18" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="K18" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>DO2</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>DO2</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="L18" s="1" t="inlineStr">
@@ -3435,11 +3255,9 @@
 9:00</t>
         </is>
       </c>
-      <c r="Q18" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="R18" s="1" t="inlineStr">
@@ -3482,18 +3300,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="W18" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
-        </is>
-      </c>
-      <c r="X18" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO2
-</t>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>DO2</t>
         </is>
       </c>
       <c r="Y18" s="1" t="inlineStr">
@@ -3512,18 +3326,14 @@
 8:11</t>
         </is>
       </c>
-      <c r="AA18" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="AB18" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="AC18" s="1" t="inlineStr">
@@ -3554,11 +3364,9 @@
           <t>許逸民</t>
         </is>
       </c>
-      <c r="C19" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="D19" s="1" t="inlineStr">
@@ -3571,17 +3379,15 @@
       </c>
       <c r="E19" s="1" t="inlineStr">
         <is>
-          <t>3:52
-ND0016
-13:08
-9:16</t>
-        </is>
-      </c>
-      <c r="F19" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+          <t>3:47
+ND0020
+13:13
+9:26</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="G19" s="1" t="inlineStr">
@@ -3600,11 +3406,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="I19" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO2
-</t>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>DO2</t>
         </is>
       </c>
       <c r="J19" s="1" t="inlineStr">
@@ -3615,11 +3419,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="K19" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="L19" s="1" t="inlineStr">
@@ -3646,11 +3448,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="O19" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="P19" s="1" t="inlineStr">
@@ -3685,11 +3485,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="T19" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="U19" s="1" t="inlineStr">
@@ -3708,18 +3506,14 @@
 9:41</t>
         </is>
       </c>
-      <c r="W19" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
-        </is>
-      </c>
-      <c r="X19" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO2
-</t>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>DO2</t>
         </is>
       </c>
       <c r="Y19" s="1" t="inlineStr">
@@ -3754,18 +3548,14 @@
 8:06</t>
         </is>
       </c>
-      <c r="AC19" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="AD19" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
     </row>
@@ -3798,7 +3588,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>DO3X</t>
+          <t>DO1</t>
         </is>
       </c>
       <c r="F20" s="1" t="inlineStr">
@@ -3809,11 +3599,9 @@
 9:38</t>
         </is>
       </c>
-      <c r="G20" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="H20" s="1" t="inlineStr">
@@ -3849,18 +3637,14 @@
 8:53</t>
         </is>
       </c>
-      <c r="L20" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="M20" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="N20" s="1" t="inlineStr">
@@ -3903,18 +3687,14 @@
 10:00</t>
         </is>
       </c>
-      <c r="S20" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="T20" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="U20" s="1" t="inlineStr">
@@ -3958,18 +3738,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="Z20" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="AA20" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="AB20" s="1" t="inlineStr">
@@ -4026,10 +3802,10 @@
       </c>
       <c r="E21" s="1" t="inlineStr">
         <is>
-          <t>8:30
-H9
-17:30
-8:00</t>
+          <t>7:02
+ND0044
+16:58
+9:56</t>
         </is>
       </c>
       <c r="F21" s="1" t="inlineStr">
@@ -4040,25 +3816,19 @@
 8:00</t>
         </is>
       </c>
-      <c r="G21" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="H21" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
-        </is>
-      </c>
-      <c r="I21" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO2
-</t>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>DO2</t>
         </is>
       </c>
       <c r="J21" s="1" t="inlineStr">
@@ -4093,32 +3863,24 @@
 8:00</t>
         </is>
       </c>
-      <c r="N21" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="O21" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
-        </is>
-      </c>
-      <c r="P21" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO2
-</t>
-        </is>
-      </c>
-      <c r="Q21" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>DO2</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="R21" s="1" t="inlineStr">
@@ -4153,25 +3915,19 @@
 8:00</t>
         </is>
       </c>
-      <c r="V21" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
-        </is>
-      </c>
-      <c r="W21" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO2
-</t>
-        </is>
-      </c>
-      <c r="X21" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO2
-</t>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>DO2</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>DO2</t>
         </is>
       </c>
       <c r="Y21" s="1" t="inlineStr">
@@ -4206,18 +3962,14 @@
 8:31</t>
         </is>
       </c>
-      <c r="AC21" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="AD21" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
     </row>
@@ -4232,23 +3984,22 @@
           <t>吳建昇</t>
         </is>
       </c>
-      <c r="C22" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="E22" s="1" t="inlineStr">
+        <is>
+          <t>3:52
+ND0016
+13:08
+9:16</t>
         </is>
       </c>
       <c r="F22" s="1" t="inlineStr">
@@ -4284,11 +4035,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="J22" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="K22" s="1" t="inlineStr">
@@ -4323,11 +4072,9 @@
 9:01</t>
         </is>
       </c>
-      <c r="O22" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="P22" s="1" t="inlineStr">
@@ -4362,18 +4109,14 @@
 10:00</t>
         </is>
       </c>
-      <c r="T22" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="U22" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="V22" s="1" t="inlineStr">
@@ -4409,18 +4152,14 @@
 9:21</t>
         </is>
       </c>
-      <c r="Z22" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="AA22" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="AB22" s="1" t="inlineStr">
@@ -4477,24 +4216,20 @@
       </c>
       <c r="E23" s="1" t="inlineStr">
         <is>
-          <t>14:57
-ND0566
-24:35
-9:38</t>
-        </is>
-      </c>
-      <c r="F23" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="G23" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+          <t>8:17
+ND0079
+17:13
+8:56</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="H23" s="1" t="inlineStr">
@@ -4530,18 +4265,14 @@
 8:06</t>
         </is>
       </c>
-      <c r="L23" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="M23" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="N23" s="1" t="inlineStr">
@@ -4576,11 +4307,9 @@
 9:11</t>
         </is>
       </c>
-      <c r="R23" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="S23" s="1" t="inlineStr">
@@ -4615,11 +4344,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="W23" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="X23" s="1" t="inlineStr">
@@ -4655,18 +4382,14 @@
 9:38</t>
         </is>
       </c>
-      <c r="AB23" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="AC23" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="AD23" s="1" t="inlineStr">
@@ -4705,9 +4428,12 @@
 8:00</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="E24" s="1" t="inlineStr">
+        <is>
+          <t>14:57
+ND0566
+24:35
+9:38</t>
         </is>
       </c>
       <c r="F24" s="1" t="inlineStr">
@@ -4718,25 +4444,19 @@
 9:16</t>
         </is>
       </c>
-      <c r="G24" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="H24" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
-        </is>
-      </c>
-      <c r="I24" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO2
-</t>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>DO2</t>
         </is>
       </c>
       <c r="J24" s="1" t="inlineStr">
@@ -4779,25 +4499,19 @@
 8:00</t>
         </is>
       </c>
-      <c r="O24" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="P24" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
-        </is>
-      </c>
-      <c r="Q24" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="R24" s="1" t="inlineStr">
@@ -4824,11 +4538,9 @@
 9:01</t>
         </is>
       </c>
-      <c r="U24" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="V24" s="1" t="inlineStr">
@@ -4847,11 +4559,9 @@
 8:16</t>
         </is>
       </c>
-      <c r="X24" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO2
-</t>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>DO2</t>
         </is>
       </c>
       <c r="Y24" s="1" t="inlineStr">
@@ -4870,18 +4580,14 @@
 9:51</t>
         </is>
       </c>
-      <c r="AA24" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="AB24" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="AC24" s="1" t="inlineStr">
@@ -4928,23 +4634,22 @@
 9:30</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-      <c r="F25" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="G25" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="E25" s="1" t="inlineStr">
+        <is>
+          <t>8:30
+FAC
+17:30
+8:00</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="H25" s="1" t="inlineStr">
@@ -4988,18 +4693,14 @@
 8:01</t>
         </is>
       </c>
-      <c r="M25" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="N25" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="O25" s="1" t="inlineStr">
@@ -5034,18 +4735,14 @@
 8:11</t>
         </is>
       </c>
-      <c r="S25" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="T25" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="U25" s="1" t="inlineStr">
@@ -5089,18 +4786,14 @@
 8:36</t>
         </is>
       </c>
-      <c r="Z25" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="AA25" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="AB25" s="1" t="inlineStr">
@@ -5157,10 +4850,10 @@
       </c>
       <c r="E26" s="1" t="inlineStr">
         <is>
-          <t>7:12
-ND0088
-16:13
-9:01</t>
+          <t>6:22
+ND0007
+14:22
+8:00</t>
         </is>
       </c>
       <c r="F26" s="1" t="inlineStr">
@@ -5171,18 +4864,14 @@
 9:56</t>
         </is>
       </c>
-      <c r="G26" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="H26" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="I26" s="1" t="inlineStr">
@@ -5210,11 +4899,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="L26" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="M26" s="1" t="inlineStr">
@@ -5241,11 +4928,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="P26" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="Q26" s="1" t="inlineStr">
@@ -5264,18 +4949,14 @@
 9:21</t>
         </is>
       </c>
-      <c r="S26" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="T26" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="U26" s="1" t="inlineStr">
@@ -5311,11 +4992,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="Y26" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="Z26" s="1" t="inlineStr">
@@ -5350,11 +5029,9 @@
 9:11</t>
         </is>
       </c>
-      <c r="AD26" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="AD26" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
     </row>
@@ -5385,19 +5062,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="E27" s="1" t="inlineStr">
-        <is>
-          <t>7:02
-ND0044
-16:58
-9:56</t>
-        </is>
-      </c>
-      <c r="F27" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="G27" s="1" t="inlineStr">
@@ -5433,11 +5105,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="K27" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="L27" s="1" t="inlineStr">
@@ -5456,11 +5126,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="N27" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="O27" s="1" t="inlineStr">
@@ -5487,18 +5155,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="R27" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="S27" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="T27" s="1" t="inlineStr">
@@ -5542,11 +5206,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="Y27" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="Z27" s="1" t="inlineStr">
@@ -5581,11 +5243,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="AD27" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="AD27" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
     </row>
@@ -5621,11 +5281,9 @@
           <t>DO1</t>
         </is>
       </c>
-      <c r="F28" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="G28" s="1" t="inlineStr">
@@ -5653,11 +5311,9 @@
 9:56</t>
         </is>
       </c>
-      <c r="J28" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="K28" s="1" t="inlineStr">
@@ -5692,11 +5348,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="O28" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="P28" s="1" t="inlineStr">
@@ -5715,11 +5369,9 @@
 8:51</t>
         </is>
       </c>
-      <c r="R28" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="S28" s="1" t="inlineStr">
@@ -5738,11 +5390,9 @@
 9:26</t>
         </is>
       </c>
-      <c r="U28" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="V28" s="1" t="inlineStr">
@@ -5786,11 +5436,9 @@
 9:26</t>
         </is>
       </c>
-      <c r="AA28" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="AB28" s="1" t="inlineStr">
@@ -5801,11 +5449,9 @@
 8:06</t>
         </is>
       </c>
-      <c r="AC28" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="AD28" s="1" t="inlineStr">
@@ -5828,11 +5474,9 @@
           <t>牟君航</t>
         </is>
       </c>
-      <c r="C29" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="D29" s="1" t="inlineStr">
@@ -5845,10 +5489,10 @@
       </c>
       <c r="E29" s="1" t="inlineStr">
         <is>
-          <t>8:17
-ND0079
-17:13
-8:56</t>
+          <t>16:30
+STD6
+24:30
+8:00</t>
         </is>
       </c>
       <c r="F29" s="1" t="inlineStr">
@@ -5859,11 +5503,9 @@
 9:16</t>
         </is>
       </c>
-      <c r="G29" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="H29" s="1" t="inlineStr">
@@ -5907,18 +5549,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="M29" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="N29" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="O29" s="1" t="inlineStr">
@@ -5961,18 +5599,14 @@
 8:01</t>
         </is>
       </c>
-      <c r="T29" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="U29" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="V29" s="1" t="inlineStr">
@@ -5991,18 +5625,14 @@
 8:38</t>
         </is>
       </c>
-      <c r="X29" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO2
-</t>
-        </is>
-      </c>
-      <c r="Y29" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>DO2</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="Z29" s="1" t="inlineStr">
@@ -6021,11 +5651,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="AB29" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="AC29" s="1" t="inlineStr">
@@ -6056,11 +5684,9 @@
           <t>彭權靖</t>
         </is>
       </c>
-      <c r="C30" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="D30" s="1" t="inlineStr">
@@ -6073,10 +5699,10 @@
       </c>
       <c r="E30" s="1" t="inlineStr">
         <is>
-          <t>3:47
-ND0020
-13:13
-9:26</t>
+          <t>9:32
+ND0095
+17:33
+8:01</t>
         </is>
       </c>
       <c r="F30" s="1" t="inlineStr">
@@ -6095,25 +5721,19 @@
 9:46</t>
         </is>
       </c>
-      <c r="H30" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
-        </is>
-      </c>
-      <c r="I30" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO2
-</t>
-        </is>
-      </c>
-      <c r="J30" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>DO2</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="K30" s="1" t="inlineStr">
@@ -6140,11 +5760,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="N30" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="O30" s="1" t="inlineStr">
@@ -6171,11 +5789,9 @@
 8:46</t>
         </is>
       </c>
-      <c r="R30" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="S30" s="1" t="inlineStr">
@@ -6202,11 +5818,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="V30" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="W30" s="1" t="inlineStr">
@@ -6234,11 +5848,9 @@
 9:06</t>
         </is>
       </c>
-      <c r="Z30" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="AA30" s="1" t="inlineStr">
@@ -6265,11 +5877,9 @@
 9:36</t>
         </is>
       </c>
-      <c r="AD30" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="AD30" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
     </row>
@@ -6284,11 +5894,9 @@
           <t>陳椸威</t>
         </is>
       </c>
-      <c r="C31" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="D31" s="1" t="inlineStr">
@@ -6299,9 +5907,12 @@
 8:18</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="E31" s="1" t="inlineStr">
+        <is>
+          <t>16:32
+ND0590
+25:00
+8:28</t>
         </is>
       </c>
       <c r="F31" s="1" t="inlineStr">
@@ -6312,11 +5923,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="G31" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="H31" s="1" t="inlineStr">
@@ -6327,11 +5936,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="I31" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO2
-</t>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>DO2</t>
         </is>
       </c>
       <c r="J31" s="1" t="inlineStr">
@@ -6350,11 +5957,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="L31" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="M31" s="1" t="inlineStr">
@@ -6381,11 +5986,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="P31" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="Q31" s="1" t="inlineStr">
@@ -6404,11 +6007,9 @@
 9:16</t>
         </is>
       </c>
-      <c r="S31" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="T31" s="1" t="inlineStr">
@@ -6435,18 +6036,14 @@
 8:58</t>
         </is>
       </c>
-      <c r="W31" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
-        </is>
-      </c>
-      <c r="X31" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO2
-</t>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>DO2</t>
         </is>
       </c>
       <c r="Y31" s="1" t="inlineStr">
@@ -6457,18 +6054,14 @@
 8:03</t>
         </is>
       </c>
-      <c r="Z31" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="AA31" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="AB31" s="1" t="inlineStr">
@@ -6523,23 +6116,22 @@
 9:21</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="F32" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="G32" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="E32" s="1" t="inlineStr">
+        <is>
+          <t>8:12
+ND0057
+16:12
+8:00</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="H32" s="1" t="inlineStr">
@@ -6575,18 +6167,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="L32" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="M32" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="N32" s="1" t="inlineStr">
@@ -6613,11 +6201,9 @@
 9:56</t>
         </is>
       </c>
-      <c r="Q32" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="R32" s="1" t="inlineStr">
@@ -6644,11 +6230,9 @@
 8:56</t>
         </is>
       </c>
-      <c r="U32" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="V32" s="1" t="inlineStr">
@@ -6692,18 +6276,14 @@
 9:01</t>
         </is>
       </c>
-      <c r="AA32" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="AB32" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="AC32" s="1" t="inlineStr">
@@ -6750,19 +6330,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="E33" s="1" t="inlineStr">
-        <is>
-          <t>9:32
-ND0095
-17:33
-8:01</t>
-        </is>
-      </c>
-      <c r="F33" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="G33" s="1" t="inlineStr">
@@ -6781,11 +6356,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="I33" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO2
-</t>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>DO2</t>
         </is>
       </c>
       <c r="J33" s="1" t="inlineStr">
@@ -6796,11 +6369,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="K33" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="L33" s="1" t="inlineStr">
@@ -6827,11 +6398,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="O33" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="P33" s="1" t="inlineStr">
@@ -6866,18 +6435,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="T33" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="U33" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="V33" s="1" t="inlineStr">
@@ -6913,11 +6478,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="Z33" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="AA33" s="1" t="inlineStr">
@@ -6944,11 +6507,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="AD33" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="AD33" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
     </row>
@@ -6979,23 +6540,22 @@
 9:31</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-      <c r="F34" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="G34" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="E34" s="1" t="inlineStr">
+        <is>
+          <t>6:02
+ND0024
+14:02
+8:00</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="H34" s="1" t="inlineStr">
@@ -7006,11 +6566,9 @@
 9:16</t>
         </is>
       </c>
-      <c r="I34" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO2
-</t>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>DO2</t>
         </is>
       </c>
       <c r="J34" s="1" t="inlineStr">
@@ -7037,11 +6595,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="M34" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="N34" s="1" t="inlineStr">
@@ -7060,11 +6616,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="P34" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="Q34" s="1" t="inlineStr">
@@ -7075,11 +6629,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="R34" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="S34" s="1" t="inlineStr">
@@ -7098,11 +6650,9 @@
 8:01</t>
         </is>
       </c>
-      <c r="U34" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="V34" s="1" t="inlineStr">
@@ -7138,18 +6688,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="Z34" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="AA34" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="AB34" s="1" t="inlineStr">
@@ -7196,19 +6742,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="D35" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="E35" s="1" t="inlineStr">
-        <is>
-          <t>11:17
-ND0073
-19:17
-8:00</t>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="F35" s="1" t="inlineStr">
@@ -7235,18 +6776,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="I35" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO2
-</t>
-        </is>
-      </c>
-      <c r="J35" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>DO2</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="K35" s="1" t="inlineStr">
@@ -7265,11 +6802,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="M35" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="N35" s="1" t="inlineStr">
@@ -7320,11 +6855,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="T35" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="U35" s="1" t="inlineStr">
@@ -7335,11 +6868,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="V35" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="W35" s="1" t="inlineStr">
@@ -7391,18 +6922,14 @@
 9:26</t>
         </is>
       </c>
-      <c r="AC35" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="AD35" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="AD35" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
     </row>
@@ -7454,25 +6981,19 @@
 8:00</t>
         </is>
       </c>
-      <c r="H36" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
-        </is>
-      </c>
-      <c r="I36" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO2
-</t>
-        </is>
-      </c>
-      <c r="J36" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>DO2</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="K36" s="1" t="inlineStr">
@@ -7515,11 +7036,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="P36" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="Q36" s="1" t="inlineStr">
@@ -7546,18 +7065,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="T36" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="U36" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="V36" s="1" t="inlineStr">
@@ -7601,18 +7116,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="AA36" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="AB36" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="AC36" s="1" t="inlineStr">
@@ -7661,24 +7172,20 @@
       </c>
       <c r="E37" s="1" t="inlineStr">
         <is>
-          <t>6:02
-ND0024
-14:02
-8:00</t>
-        </is>
-      </c>
-      <c r="F37" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="G37" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+          <t>12:42
+ND0575
+22:33
+9:51</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="H37" s="1" t="inlineStr">
@@ -7706,11 +7213,9 @@
 8:16</t>
         </is>
       </c>
-      <c r="K37" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="L37" s="1" t="inlineStr">
@@ -7745,11 +7250,9 @@
 9:00</t>
         </is>
       </c>
-      <c r="P37" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="Q37" s="1" t="inlineStr">
@@ -7792,25 +7295,19 @@
 8:00</t>
         </is>
       </c>
-      <c r="V37" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="W37" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
-        </is>
-      </c>
-      <c r="X37" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO2
-</t>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>DO2</t>
         </is>
       </c>
       <c r="Y37" s="1" t="inlineStr">
@@ -7845,18 +7342,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="AC37" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="AD37" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="AD37" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
     </row>
@@ -7879,19 +7372,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="D38" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="E38" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="F38" s="1" t="inlineStr">
@@ -7918,18 +7406,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="I38" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO2
-</t>
-        </is>
-      </c>
-      <c r="J38" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>DO2</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="K38" s="1" t="inlineStr">
@@ -7948,11 +7432,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="M38" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="N38" s="1" t="inlineStr">
@@ -7995,11 +7477,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="S38" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="T38" s="1" t="inlineStr">
@@ -8026,32 +7506,24 @@
 8:00</t>
         </is>
       </c>
-      <c r="W38" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
-        </is>
-      </c>
-      <c r="X38" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO2
-</t>
-        </is>
-      </c>
-      <c r="Y38" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO2
-</t>
-        </is>
-      </c>
-      <c r="Z38" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>DO2</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>DO2</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="AA38" s="1" t="inlineStr">
@@ -8078,11 +7550,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="AD38" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="AD38" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
     </row>
@@ -8113,12 +7583,9 @@
 8:11</t>
         </is>
       </c>
-      <c r="E39" s="1" t="inlineStr">
-        <is>
-          <t>5:02
-ND0047
-14:03
-9:01</t>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="F39" s="1" t="inlineStr">
@@ -8129,11 +7596,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="G39" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="H39" s="1" t="inlineStr">
@@ -8144,11 +7609,9 @@
 8:56</t>
         </is>
       </c>
-      <c r="I39" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO2
-</t>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>DO2</t>
         </is>
       </c>
       <c r="J39" s="1" t="inlineStr">
@@ -8183,18 +7646,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="N39" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="O39" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="P39" s="1" t="inlineStr">
@@ -8221,11 +7680,9 @@
 8:16</t>
         </is>
       </c>
-      <c r="S39" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="T39" s="1" t="inlineStr">
@@ -8252,11 +7709,9 @@
 8:16</t>
         </is>
       </c>
-      <c r="W39" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="X39" s="1" t="inlineStr">
@@ -8276,11 +7731,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="Z39" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="AA39" s="1" t="inlineStr">
@@ -8291,11 +7744,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="AB39" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="AC39" s="1" t="inlineStr">
@@ -8342,19 +7793,14 @@
 9:51</t>
         </is>
       </c>
-      <c r="E40" s="1" t="inlineStr">
-        <is>
-          <t>11:30
-STD3
-19:30
-8:00</t>
-        </is>
-      </c>
-      <c r="F40" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="G40" s="1" t="inlineStr">
@@ -8398,18 +7844,14 @@
 9:51</t>
         </is>
       </c>
-      <c r="L40" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="M40" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="N40" s="1" t="inlineStr">
@@ -8436,11 +7878,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="Q40" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="R40" s="1" t="inlineStr">
@@ -8483,11 +7923,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="W40" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="X40" s="1" t="inlineStr">
@@ -8523,18 +7961,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="AB40" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="AC40" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="AD40" s="1" t="inlineStr">
@@ -8565,19 +7999,14 @@
 9:36</t>
         </is>
       </c>
-      <c r="D41" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="E41" s="1" t="inlineStr">
-        <is>
-          <t>16:32
-ND0590
-25:00
-8:28</t>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="F41" s="1" t="inlineStr">
@@ -8629,18 +8058,14 @@
 8:16</t>
         </is>
       </c>
-      <c r="L41" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="M41" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="N41" s="1" t="inlineStr">
@@ -8683,18 +8108,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="S41" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="T41" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="U41" s="1" t="inlineStr">
@@ -8738,11 +8159,9 @@
 9:51</t>
         </is>
       </c>
-      <c r="Z41" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="AA41" s="1" t="inlineStr">
@@ -8769,11 +8188,9 @@
 9:31</t>
         </is>
       </c>
-      <c r="AD41" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="AD41" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
     </row>
@@ -8804,19 +8221,14 @@
 8:41</t>
         </is>
       </c>
-      <c r="E42" s="1" t="inlineStr">
-        <is>
-          <t>14:42
-ND0530
-24:17
-9:35</t>
-        </is>
-      </c>
-      <c r="F42" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="G42" s="1" t="inlineStr">
@@ -8852,11 +8264,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="K42" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="L42" s="1" t="inlineStr">
@@ -8891,18 +8301,14 @@
 8:37</t>
         </is>
       </c>
-      <c r="P42" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
-        </is>
-      </c>
-      <c r="Q42" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="R42" s="1" t="inlineStr">
@@ -8945,18 +8351,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="W42" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
-        </is>
-      </c>
-      <c r="X42" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO2
-</t>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>DO2</t>
         </is>
       </c>
       <c r="Y42" s="1" t="inlineStr">
@@ -8983,18 +8385,14 @@
 10:00</t>
         </is>
       </c>
-      <c r="AB42" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="AC42" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="AD42" s="1" t="inlineStr">
@@ -9033,19 +8431,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="E43" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-H9
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="F43" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="G43" s="1" t="inlineStr">
@@ -9089,18 +8482,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="L43" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="M43" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="N43" s="1" t="inlineStr">
@@ -9127,11 +8516,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="Q43" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="R43" s="1" t="inlineStr">
@@ -9158,11 +8545,9 @@
 8:41</t>
         </is>
       </c>
-      <c r="U43" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="V43" s="1" t="inlineStr">
@@ -9181,18 +8566,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="X43" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO2
-</t>
-        </is>
-      </c>
-      <c r="Y43" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>DO2</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="Z43" s="1" t="inlineStr">
@@ -9219,11 +8600,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="AC43" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="AD43" s="1" t="inlineStr">
@@ -9267,11 +8646,9 @@
           <t>DO1</t>
         </is>
       </c>
-      <c r="F44" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="G44" s="1" t="inlineStr">
@@ -9290,11 +8667,9 @@
 10:00</t>
         </is>
       </c>
-      <c r="I44" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO2
-</t>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>DO2</t>
         </is>
       </c>
       <c r="J44" s="1" t="inlineStr">
@@ -9305,11 +8680,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="K44" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="L44" s="1" t="inlineStr">
@@ -9336,11 +8709,9 @@
 9:11</t>
         </is>
       </c>
-      <c r="O44" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="P44" s="1" t="inlineStr">
@@ -9359,11 +8730,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="R44" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="S44" s="1" t="inlineStr">
@@ -9382,11 +8751,9 @@
 8:28</t>
         </is>
       </c>
-      <c r="U44" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="V44" s="1" t="inlineStr">
@@ -9405,11 +8772,9 @@
 9:20</t>
         </is>
       </c>
-      <c r="X44" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO2
-</t>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>DO2</t>
         </is>
       </c>
       <c r="Y44" s="1" t="inlineStr">
@@ -9428,18 +8793,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="AA44" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="AB44" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="AC44" s="1" t="inlineStr">
@@ -9470,11 +8831,9 @@
           <t>江杰叡</t>
         </is>
       </c>
-      <c r="C45" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="D45" s="1" t="inlineStr">
@@ -9487,17 +8846,15 @@
       </c>
       <c r="E45" s="1" t="inlineStr">
         <is>
-          <t>6:47
-ND0028
-15:33
-8:46</t>
-        </is>
-      </c>
-      <c r="F45" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+          <t>5:02
+ND0047
+14:03
+9:01</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="G45" s="1" t="inlineStr">
@@ -9533,18 +8890,14 @@
 9:30</t>
         </is>
       </c>
-      <c r="K45" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="L45" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="M45" s="1" t="inlineStr">
@@ -9587,11 +8940,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="R45" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="S45" s="1" t="inlineStr">
@@ -9618,11 +8969,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="V45" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="W45" s="1" t="inlineStr">
@@ -9666,18 +9015,14 @@
 9:26</t>
         </is>
       </c>
-      <c r="AB45" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="AC45" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="AD45" s="1" t="inlineStr">
@@ -9700,26 +9045,22 @@
           <t>吳睿哲</t>
         </is>
       </c>
-      <c r="C46" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="D46" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="E46" s="1" t="inlineStr">
         <is>
-          <t>4:00
-STD1
-13:00
-9:00</t>
+          <t>15:22
+ND0582
+25:13
+9:51</t>
         </is>
       </c>
       <c r="F46" s="1" t="inlineStr">
@@ -9755,11 +9096,9 @@
 9:26</t>
         </is>
       </c>
-      <c r="J46" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="K46" s="1" t="inlineStr">
@@ -9802,18 +9141,14 @@
 8:26</t>
         </is>
       </c>
-      <c r="P46" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
-        </is>
-      </c>
-      <c r="Q46" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="R46" s="1" t="inlineStr">
@@ -9856,25 +9191,19 @@
 8:00</t>
         </is>
       </c>
-      <c r="W46" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
-        </is>
-      </c>
-      <c r="X46" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO2
-</t>
-        </is>
-      </c>
-      <c r="Y46" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>DO2</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="Z46" s="1" t="inlineStr">
@@ -9909,11 +9238,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="AD46" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="AD46" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
     </row>
@@ -9928,11 +9255,9 @@
           <t>吳子昌</t>
         </is>
       </c>
-      <c r="C47" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="D47" s="1" t="inlineStr">
@@ -9967,11 +9292,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="H47" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="I47" s="1" t="inlineStr">
@@ -9983,18 +9306,14 @@
 9:01</t>
         </is>
       </c>
-      <c r="J47" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="K47" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="L47" s="1" t="inlineStr">
@@ -10045,18 +9364,14 @@
 9:21</t>
         </is>
       </c>
-      <c r="R47" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="S47" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="T47" s="1" t="inlineStr">
@@ -10100,11 +9415,9 @@
 8:11</t>
         </is>
       </c>
-      <c r="Y47" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="Z47" s="1" t="inlineStr">
@@ -10139,11 +9452,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="AD47" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="AD47" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
     </row>
@@ -10158,11 +9469,9 @@
           <t>江之聖</t>
         </is>
       </c>
-      <c r="C48" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="D48" s="1" t="inlineStr">
@@ -10173,9 +9482,12 @@
 8:56</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="E48" s="1" t="inlineStr">
+        <is>
+          <t>4:02
+ND0003
+12:58
+8:56</t>
         </is>
       </c>
       <c r="F48" s="1" t="inlineStr">
@@ -10194,11 +9506,9 @@
 9:01</t>
         </is>
       </c>
-      <c r="H48" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="I48" s="1" t="inlineStr">
@@ -10226,18 +9536,14 @@
 9:30</t>
         </is>
       </c>
-      <c r="L48" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="M48" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="N48" s="1" t="inlineStr">
@@ -10272,11 +9578,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="R48" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="S48" s="1" t="inlineStr">
@@ -10303,11 +9607,9 @@
 8:06</t>
         </is>
       </c>
-      <c r="V48" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="W48" s="1" t="inlineStr">
@@ -10335,18 +9637,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="Z48" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="AA48" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="AB48" s="1" t="inlineStr">
@@ -10393,16 +9691,14 @@
 9:41</t>
         </is>
       </c>
-      <c r="D49" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>DO1</t>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="F49" s="1" t="inlineStr">
@@ -10429,11 +9725,9 @@
 9:06</t>
         </is>
       </c>
-      <c r="I49" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO2
-</t>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>DO2</t>
         </is>
       </c>
       <c r="J49" s="1" t="inlineStr">
@@ -10452,18 +9746,14 @@
 9:26</t>
         </is>
       </c>
-      <c r="L49" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="M49" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="N49" s="1" t="inlineStr">
@@ -10506,11 +9796,9 @@
 8:06</t>
         </is>
       </c>
-      <c r="S49" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="T49" s="1" t="inlineStr">
@@ -10529,11 +9817,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="V49" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="W49" s="1" t="inlineStr">
@@ -10568,18 +9854,14 @@
 9:38</t>
         </is>
       </c>
-      <c r="AA49" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="AB49" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="AC49" s="1" t="inlineStr">
@@ -10618,19 +9900,14 @@
 10:00</t>
         </is>
       </c>
-      <c r="D50" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="E50" s="1" t="inlineStr">
-        <is>
-          <t>8:12
-ND0057
-16:12
-8:00</t>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="F50" s="1" t="inlineStr">
@@ -10674,11 +9951,9 @@
 8:41</t>
         </is>
       </c>
-      <c r="K50" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="L50" s="1" t="inlineStr">
@@ -10713,11 +9988,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="P50" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="Q50" s="1" t="inlineStr">
@@ -10760,32 +10033,24 @@
 8:00</t>
         </is>
       </c>
-      <c r="V50" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="W50" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
-        </is>
-      </c>
-      <c r="X50" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO2
-</t>
-        </is>
-      </c>
-      <c r="Y50" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>DO2</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="Z50" s="1" t="inlineStr">
@@ -10820,11 +10085,9 @@
 8:26</t>
         </is>
       </c>
-      <c r="AD50" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="AD50" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
     </row>
@@ -10857,24 +10120,20 @@
       </c>
       <c r="E51" s="1" t="inlineStr">
         <is>
-          <t>4:02
-ND0003
-12:58
-8:56</t>
-        </is>
-      </c>
-      <c r="F51" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="G51" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+          <t>16:22
+ND0588
+24:38
+8:16</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="H51" s="1" t="inlineStr">
@@ -10902,11 +10161,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="K51" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="L51" s="1" t="inlineStr">
@@ -10941,25 +10198,19 @@
 8:01</t>
         </is>
       </c>
-      <c r="P51" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
-        </is>
-      </c>
-      <c r="Q51" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="R51" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="S51" s="1" t="inlineStr">
@@ -11002,18 +10253,14 @@
 8:36</t>
         </is>
       </c>
-      <c r="X51" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO2
-</t>
-        </is>
-      </c>
-      <c r="Y51" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>DO2</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="Z51" s="1" t="inlineStr">
@@ -11048,11 +10295,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="AD51" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="AD51" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
     </row>
@@ -11083,16 +10328,17 @@
 8:56</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-      <c r="F52" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="E52" s="1" t="inlineStr">
+        <is>
+          <t>6:47
+ND0028
+15:33
+8:46</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="G52" s="1" t="inlineStr">
@@ -11103,18 +10349,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="H52" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
-        </is>
-      </c>
-      <c r="I52" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO2
-</t>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>DO2</t>
         </is>
       </c>
       <c r="J52" s="1" t="inlineStr">
@@ -11141,18 +10383,14 @@
 9:26</t>
         </is>
       </c>
-      <c r="M52" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="N52" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="O52" s="1" t="inlineStr">
@@ -11195,11 +10433,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="T52" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="U52" s="1" t="inlineStr">
@@ -11218,11 +10454,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="W52" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="X52" s="1" t="inlineStr">
@@ -11242,18 +10476,14 @@
 8:06</t>
         </is>
       </c>
-      <c r="Z52" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="AA52" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="AB52" s="1" t="inlineStr">
@@ -11300,19 +10530,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="D53" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="E53" s="1" t="inlineStr">
-        <is>
-          <t>4:42
-ND0014
-12:42
-8:00</t>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="F53" s="1" t="inlineStr">
@@ -11356,11 +10581,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="K53" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="L53" s="1" t="inlineStr">
@@ -11387,11 +10610,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="O53" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="P53" s="1" t="inlineStr">
@@ -11418,11 +10639,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="S53" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="T53" s="1" t="inlineStr">
@@ -11449,11 +10668,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="W53" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="X53" s="1" t="inlineStr">
@@ -11489,18 +10706,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="AB53" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="AC53" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="AD53" s="1" t="inlineStr">
@@ -11531,16 +10744,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="D54" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>DO1</t>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="F54" s="1" t="inlineStr">
@@ -11584,11 +10795,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="K54" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="L54" s="1" t="inlineStr">
@@ -11623,11 +10832,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="P54" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="Q54" s="1" t="inlineStr">
@@ -11646,18 +10853,14 @@
 8:41</t>
         </is>
       </c>
-      <c r="S54" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="T54" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="U54" s="1" t="inlineStr">
@@ -11684,11 +10887,9 @@
 8:31</t>
         </is>
       </c>
-      <c r="X54" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO2
-</t>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>DO2</t>
         </is>
       </c>
       <c r="Y54" s="1" t="inlineStr">
@@ -11707,18 +10908,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="AA54" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="AB54" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="AC54" s="1" t="inlineStr">
@@ -11765,19 +10962,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="E55" s="1" t="inlineStr">
-        <is>
-          <t>14:57
-ND0568
-24:35
-9:38</t>
-        </is>
-      </c>
-      <c r="F55" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="G55" s="1" t="inlineStr">
@@ -11805,11 +10997,9 @@
 9:11</t>
         </is>
       </c>
-      <c r="J55" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="K55" s="1" t="inlineStr">
@@ -11852,11 +11042,9 @@
 8:16</t>
         </is>
       </c>
-      <c r="P55" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="Q55" s="1" t="inlineStr">
@@ -11867,11 +11055,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="R55" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="S55" s="1" t="inlineStr">
@@ -11898,11 +11084,9 @@
 8:31</t>
         </is>
       </c>
-      <c r="V55" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="W55" s="1" t="inlineStr">
@@ -11946,18 +11130,14 @@
 9:01</t>
         </is>
       </c>
-      <c r="AB55" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="AC55" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="AD55" s="1" t="inlineStr">
@@ -11988,19 +11168,14 @@
 9:26</t>
         </is>
       </c>
-      <c r="D56" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="E56" s="1" t="inlineStr">
-        <is>
-          <t>16:30
-STD6
-24:30
-8:00</t>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="F56" s="1" t="inlineStr">
@@ -12044,11 +11219,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="K56" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="L56" s="1" t="inlineStr">
@@ -12083,25 +11256,19 @@
 8:46</t>
         </is>
       </c>
-      <c r="P56" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
-        </is>
-      </c>
-      <c r="Q56" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="R56" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="S56" s="1" t="inlineStr">
@@ -12153,18 +11320,14 @@
 9:36</t>
         </is>
       </c>
-      <c r="Y56" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="Z56" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="AA56" s="1" t="inlineStr">
@@ -12219,19 +11382,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="D57" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="E57" s="1" t="inlineStr">
-        <is>
-          <t>13:42
-ND0516
-23:03
-9:21</t>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="F57" s="1" t="inlineStr">
@@ -12275,11 +11433,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="K57" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="L57" s="1" t="inlineStr">
@@ -12290,11 +11446,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="M57" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="N57" s="1" t="inlineStr">
@@ -12329,11 +11483,9 @@
 8:16</t>
         </is>
       </c>
-      <c r="R57" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="S57" s="1" t="inlineStr">
@@ -12368,11 +11520,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="W57" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="X57" s="1" t="inlineStr">
@@ -12408,18 +11558,14 @@
 9:21</t>
         </is>
       </c>
-      <c r="AB57" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="AC57" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="AD57" s="1" t="inlineStr">
@@ -12460,14 +11606,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-      <c r="F58" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="G58" s="1" t="inlineStr">
@@ -12511,11 +11655,9 @@
 8:46</t>
         </is>
       </c>
-      <c r="L58" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="M58" s="1" t="inlineStr">
@@ -12542,18 +11684,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="P58" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
-        </is>
-      </c>
-      <c r="Q58" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="R58" s="1" t="inlineStr">
@@ -12580,11 +11718,9 @@
 9:56</t>
         </is>
       </c>
-      <c r="U58" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="V58" s="1" t="inlineStr">
@@ -12603,11 +11739,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="X58" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO2
-</t>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>DO2</t>
         </is>
       </c>
       <c r="Y58" s="1" t="inlineStr">
@@ -12618,18 +11752,14 @@
 8:16</t>
         </is>
       </c>
-      <c r="Z58" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="AA58" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="AB58" s="1" t="inlineStr">
@@ -12668,11 +11798,9 @@
           <t>留煒翔</t>
         </is>
       </c>
-      <c r="C59" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="D59" s="1" t="inlineStr">
@@ -12683,9 +11811,12 @@
 8:11</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="E59" s="1" t="inlineStr">
+        <is>
+          <t>14:57
+ND0568
+24:35
+9:38</t>
         </is>
       </c>
       <c r="F59" s="1" t="inlineStr">
@@ -12704,11 +11835,9 @@
 9:41</t>
         </is>
       </c>
-      <c r="H59" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="I59" s="1" t="inlineStr">
@@ -12720,11 +11849,9 @@
 8:31</t>
         </is>
       </c>
-      <c r="J59" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="K59" s="1" t="inlineStr">
@@ -12767,11 +11894,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="P59" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="Q59" s="1" t="inlineStr">
@@ -12798,18 +11923,14 @@
 9:16</t>
         </is>
       </c>
-      <c r="T59" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="U59" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="V59" s="1" t="inlineStr">
@@ -12845,18 +11966,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="Z59" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="AA59" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="AB59" s="1" t="inlineStr">
@@ -12903,19 +12020,17 @@
 9:11</t>
         </is>
       </c>
-      <c r="D60" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="E60" s="1" t="inlineStr">
         <is>
-          <t>15:22
-ND0582
-25:13
-9:51</t>
+          <t>14:13
+ND0564
+22:13
+8:00</t>
         </is>
       </c>
       <c r="F60" s="1" t="inlineStr">
@@ -12934,18 +12049,14 @@
 8:41</t>
         </is>
       </c>
-      <c r="H60" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
-        </is>
-      </c>
-      <c r="I60" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO2
-</t>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>DO2</t>
         </is>
       </c>
       <c r="J60" s="1" t="inlineStr">
@@ -12972,18 +12083,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="M60" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="N60" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="O60" s="1" t="inlineStr">
@@ -13018,11 +12125,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="S60" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="T60" s="1" t="inlineStr">
@@ -13049,11 +12154,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="W60" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="X60" s="1" t="inlineStr">
@@ -13097,18 +12200,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="AC60" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="AD60" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="AD60" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
     </row>
@@ -13131,19 +12230,14 @@
 8:16</t>
         </is>
       </c>
-      <c r="D61" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="E61" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="F61" s="1" t="inlineStr">
@@ -13187,11 +12281,9 @@
 8:06</t>
         </is>
       </c>
-      <c r="K61" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="L61" s="1" t="inlineStr">
@@ -13226,11 +12318,9 @@
 9:45</t>
         </is>
       </c>
-      <c r="P61" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="Q61" s="1" t="inlineStr">
@@ -13273,32 +12363,24 @@
 8:00</t>
         </is>
       </c>
-      <c r="V61" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="W61" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
-        </is>
-      </c>
-      <c r="X61" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO2
-</t>
-        </is>
-      </c>
-      <c r="Y61" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>DO2</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="Z61" s="1" t="inlineStr">
@@ -13325,11 +12407,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="AC61" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="AD61" s="1" t="inlineStr">
@@ -13352,23 +12432,22 @@
           <t>李俊賢</t>
         </is>
       </c>
-      <c r="C62" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="D62" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="E62" s="1" t="inlineStr">
+        <is>
+          <t>14:42
+ND0530
+24:17
+9:35</t>
         </is>
       </c>
       <c r="F62" s="1" t="inlineStr">
@@ -13412,11 +12491,9 @@
 9:21</t>
         </is>
       </c>
-      <c r="K62" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="L62" s="1" t="inlineStr">
@@ -13443,11 +12520,9 @@
 9:21</t>
         </is>
       </c>
-      <c r="O62" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="P62" s="1" t="inlineStr">
@@ -13474,18 +12549,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="S62" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="T62" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="U62" s="1" t="inlineStr">
@@ -13529,18 +12600,14 @@
 10:00</t>
         </is>
       </c>
-      <c r="Z62" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="AA62" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="AB62" s="1" t="inlineStr">
@@ -13595,16 +12662,17 @@
 9:40</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="F63" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="E63" s="1" t="inlineStr">
+        <is>
+          <t>12:32
+ND0502
+21:13
+8:41</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="G63" s="1" t="inlineStr">
@@ -13657,18 +12725,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="M63" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="N63" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="O63" s="1" t="inlineStr">
@@ -13703,18 +12767,14 @@
 8:31</t>
         </is>
       </c>
-      <c r="S63" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="T63" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="U63" s="1" t="inlineStr">
@@ -13766,11 +12826,9 @@
 9:36</t>
         </is>
       </c>
-      <c r="AA63" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="AB63" s="1" t="inlineStr">
@@ -13789,11 +12847,9 @@
 8:37</t>
         </is>
       </c>
-      <c r="AD63" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="AD63" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
     </row>
@@ -13816,19 +12872,14 @@
 8:06</t>
         </is>
       </c>
-      <c r="D64" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="E64" s="1" t="inlineStr">
-        <is>
-          <t>12:42
-ND0575
-22:33
-9:51</t>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="F64" s="1" t="inlineStr">
@@ -13855,11 +12906,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="I64" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO2
-</t>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>DO2</t>
         </is>
       </c>
       <c r="J64" s="1" t="inlineStr">
@@ -13870,11 +12919,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="K64" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="L64" s="1" t="inlineStr">
@@ -13901,11 +12948,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="O64" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="P64" s="1" t="inlineStr">
@@ -13940,18 +12985,14 @@
 9:16</t>
         </is>
       </c>
-      <c r="T64" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="U64" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="V64" s="1" t="inlineStr">
@@ -13979,11 +13020,9 @@
 8:16</t>
         </is>
       </c>
-      <c r="Y64" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="Z64" s="1" t="inlineStr">
@@ -14002,11 +13041,9 @@
 9:51</t>
         </is>
       </c>
-      <c r="AB64" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="AC64" s="1" t="inlineStr">

--- a/data/TTN/最新版班表/2026-10/TTN_TD.xlsx
+++ b/data/TTN/最新版班表/2026-10/TTN_TD.xlsx
@@ -882,9 +882,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="D7" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="E7" s="1" t="inlineStr">
@@ -911,19 +913,25 @@
 8:16</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>DO2</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="H7" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
+        </is>
+      </c>
+      <c r="I7" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO2
+</t>
+        </is>
+      </c>
+      <c r="J7" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="K7" s="1" t="inlineStr">
@@ -958,9 +966,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="O7" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="P7" s="1" t="inlineStr">
@@ -987,14 +997,18 @@
 8:38</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="S7" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="T7" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="U7" s="1" t="inlineStr">
@@ -1038,14 +1052,18 @@
 8:00</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="Z7" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="AA7" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="AB7" s="1" t="inlineStr">
@@ -1084,9 +1102,11 @@
           <t>林行憲</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="C8" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="D8" s="1" t="inlineStr">
@@ -1113,9 +1133,11 @@
 9:00</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="G8" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="H8" s="1" t="inlineStr">
@@ -1126,14 +1148,18 @@
 8:00</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>DO2</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="I8" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO2
+</t>
+        </is>
+      </c>
+      <c r="J8" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="K8" s="1" t="inlineStr">
@@ -1185,9 +1211,11 @@
 9:00</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="Q8" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="R8" s="1" t="inlineStr">
@@ -1230,14 +1258,18 @@
 9:00</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>DO2</t>
+      <c r="W8" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
+        </is>
+      </c>
+      <c r="X8" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO2
+</t>
         </is>
       </c>
       <c r="Y8" s="1" t="inlineStr">
@@ -1281,9 +1313,11 @@
 9:00</t>
         </is>
       </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="AD8" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
     </row>
@@ -1306,9 +1340,11 @@
 9:26</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="D9" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="E9" s="1" t="inlineStr">
@@ -1335,9 +1371,11 @@
 8:11</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="H9" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="I9" s="1" t="inlineStr">
@@ -1373,14 +1411,18 @@
 9:20</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="M9" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="N9" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="O9" s="1" t="inlineStr">
@@ -1415,9 +1457,11 @@
 9:51</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="S9" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="T9" s="1" t="inlineStr">
@@ -1436,9 +1480,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="V9" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="W9" s="1" t="inlineStr">
@@ -1482,14 +1528,18 @@
 9:51</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="AB9" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="AC9" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="AD9" s="1" t="inlineStr">
@@ -1512,14 +1562,18 @@
           <t>李國維</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="C10" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="E10" s="1" t="inlineStr">
@@ -1554,14 +1608,18 @@
 9:26</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>DO2</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="I10" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO2
+</t>
+        </is>
+      </c>
+      <c r="J10" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="K10" s="1" t="inlineStr">
@@ -1596,9 +1654,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="O10" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="P10" s="1" t="inlineStr">
@@ -1633,19 +1693,25 @@
 8:00</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>DO2</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="T10" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO2
+</t>
+        </is>
+      </c>
+      <c r="U10" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="V10" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="W10" s="1" t="inlineStr">
@@ -1681,14 +1747,18 @@
 8:00</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="AA10" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="AB10" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="AC10" s="1" t="inlineStr">
@@ -1727,9 +1797,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="D11" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="E11" s="1" t="inlineStr">
@@ -1748,9 +1820,11 @@
 8:41</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="G11" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="H11" s="1" t="inlineStr">
@@ -1786,14 +1860,18 @@
 9:51</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="L11" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="M11" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="N11" s="1" t="inlineStr">
@@ -1820,9 +1898,11 @@
 8:21</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="Q11" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="R11" s="1" t="inlineStr">
@@ -1857,9 +1937,11 @@
 8:51</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="V11" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="W11" s="1" t="inlineStr">
@@ -1895,14 +1977,18 @@
 8:00</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="AA11" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="AB11" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="AC11" s="1" t="inlineStr">
@@ -1965,19 +2051,25 @@
 8:00</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>DO2</t>
+      <c r="G12" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="H12" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
+        </is>
+      </c>
+      <c r="I12" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO2
+</t>
         </is>
       </c>
       <c r="J12" s="1" t="inlineStr">
@@ -1996,14 +2088,18 @@
 8:00</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="L12" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="M12" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="N12" s="1" t="inlineStr">
@@ -2038,19 +2134,25 @@
 8:00</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>DO2</t>
+      <c r="R12" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="S12" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
+        </is>
+      </c>
+      <c r="T12" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO2
+</t>
         </is>
       </c>
       <c r="U12" s="1" t="inlineStr">
@@ -2086,14 +2188,18 @@
 8:00</t>
         </is>
       </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="Y12" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="Z12" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="AA12" s="1" t="inlineStr">
@@ -2140,9 +2246,11 @@
           <t>程耀輝</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="C13" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="D13" s="1" t="inlineStr">
@@ -2177,14 +2285,18 @@
 8:06</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>DO2</t>
+      <c r="H13" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
+        </is>
+      </c>
+      <c r="I13" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO2
+</t>
         </is>
       </c>
       <c r="J13" s="1" t="inlineStr">
@@ -2227,14 +2339,18 @@
 8:00</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="O13" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="P13" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="Q13" s="1" t="inlineStr">
@@ -2245,14 +2361,18 @@
 8:00</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="R13" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="S13" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="T13" s="1" t="inlineStr">
@@ -2296,14 +2416,18 @@
 9:01</t>
         </is>
       </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="Y13" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="Z13" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="AA13" s="1" t="inlineStr">
@@ -2358,9 +2482,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="D14" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="E14" s="1" t="inlineStr">
@@ -2371,9 +2497,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="F14" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="G14" s="1" t="inlineStr">
@@ -2392,9 +2520,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>DO2</t>
+      <c r="I14" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO2
+</t>
         </is>
       </c>
       <c r="J14" s="1" t="inlineStr">
@@ -2405,9 +2535,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="K14" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="L14" s="1" t="inlineStr">
@@ -2442,9 +2574,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="P14" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="Q14" s="1" t="inlineStr">
@@ -2471,14 +2605,18 @@
 8:00</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="T14" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="U14" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="V14" s="1" t="inlineStr">
@@ -2514,9 +2652,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="Z14" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="AA14" s="1" t="inlineStr">
@@ -2543,9 +2683,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="AD14" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="AD14" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
     </row>
@@ -2753,9 +2895,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="D16" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="E16" s="1" t="inlineStr">
@@ -2782,14 +2926,18 @@
 8:00</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>DO2</t>
+      <c r="H16" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
+        </is>
+      </c>
+      <c r="I16" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO2
+</t>
         </is>
       </c>
       <c r="J16" s="1" t="inlineStr">
@@ -2824,14 +2972,18 @@
 9:38</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="N16" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="O16" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="P16" s="1" t="inlineStr">
@@ -2874,14 +3026,18 @@
 8:00</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="U16" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="V16" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="W16" s="1" t="inlineStr">
@@ -2933,14 +3089,18 @@
 8:00</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="AD16" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="AC16" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="AD16" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
     </row>
@@ -2955,9 +3115,11 @@
           <t>袁皓威</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="C17" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="D17" s="1" t="inlineStr">
@@ -2992,19 +3154,25 @@
 8:00</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>DO2</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="H17" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
+        </is>
+      </c>
+      <c r="I17" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO2
+</t>
+        </is>
+      </c>
+      <c r="J17" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="K17" s="1" t="inlineStr">
@@ -3047,14 +3215,18 @@
 8:00</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="P17" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
+        </is>
+      </c>
+      <c r="Q17" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="R17" s="1" t="inlineStr">
@@ -3097,19 +3269,25 @@
 8:00</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>DO2</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="W17" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
+        </is>
+      </c>
+      <c r="X17" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO2
+</t>
+        </is>
+      </c>
+      <c r="Y17" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="Z17" s="1" t="inlineStr">
@@ -3144,9 +3322,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="AD17" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="AD17" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
     </row>
@@ -3169,9 +3349,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="D18" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="E18" s="1" t="inlineStr">
@@ -3190,29 +3372,39 @@
 9:00</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>DO2</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>DO2</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="G18" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO2
+</t>
+        </is>
+      </c>
+      <c r="H18" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
+        </is>
+      </c>
+      <c r="I18" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO2
+</t>
+        </is>
+      </c>
+      <c r="J18" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="K18" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="L18" s="1" t="inlineStr">
@@ -3255,9 +3447,11 @@
 9:00</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="Q18" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="R18" s="1" t="inlineStr">
@@ -3300,14 +3494,18 @@
 8:00</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>DO2</t>
+      <c r="W18" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
+        </is>
+      </c>
+      <c r="X18" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO2
+</t>
         </is>
       </c>
       <c r="Y18" s="1" t="inlineStr">
@@ -3326,14 +3524,18 @@
 8:11</t>
         </is>
       </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="AA18" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="AB18" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="AC18" s="1" t="inlineStr">
@@ -3364,9 +3566,11 @@
           <t>許逸民</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="C19" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="D19" s="1" t="inlineStr">
@@ -3385,9 +3589,11 @@
 9:26</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="F19" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="G19" s="1" t="inlineStr">
@@ -3406,9 +3612,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>DO2</t>
+      <c r="I19" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO2
+</t>
         </is>
       </c>
       <c r="J19" s="1" t="inlineStr">
@@ -3419,9 +3627,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="K19" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="L19" s="1" t="inlineStr">
@@ -3448,9 +3658,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="O19" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="P19" s="1" t="inlineStr">
@@ -3485,9 +3697,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="T19" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="U19" s="1" t="inlineStr">
@@ -3506,14 +3720,18 @@
 9:41</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>DO2</t>
+      <c r="W19" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
+        </is>
+      </c>
+      <c r="X19" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO2
+</t>
         </is>
       </c>
       <c r="Y19" s="1" t="inlineStr">
@@ -3548,14 +3766,18 @@
 8:06</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="AD19" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="AC19" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="AD19" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
     </row>
@@ -3586,9 +3808,11 @@
 8:13</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="E20" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="F20" s="1" t="inlineStr">
@@ -3599,9 +3823,11 @@
 9:38</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="G20" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="H20" s="1" t="inlineStr">
@@ -3637,14 +3863,18 @@
 8:53</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="L20" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="M20" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="N20" s="1" t="inlineStr">
@@ -3687,14 +3917,18 @@
 10:00</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="S20" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="T20" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="U20" s="1" t="inlineStr">
@@ -3738,14 +3972,18 @@
 8:00</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="AA20" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="Z20" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="AA20" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="AB20" s="1" t="inlineStr">
@@ -3816,19 +4054,25 @@
 8:00</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>DO2</t>
+      <c r="G21" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="H21" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
+        </is>
+      </c>
+      <c r="I21" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO2
+</t>
         </is>
       </c>
       <c r="J21" s="1" t="inlineStr">
@@ -3863,24 +4107,32 @@
 8:00</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>DO2</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="N21" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="O21" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
+        </is>
+      </c>
+      <c r="P21" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO2
+</t>
+        </is>
+      </c>
+      <c r="Q21" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="R21" s="1" t="inlineStr">
@@ -3915,19 +4167,25 @@
 8:00</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>DO2</t>
-        </is>
-      </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>DO2</t>
+      <c r="V21" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
+        </is>
+      </c>
+      <c r="W21" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO2
+</t>
+        </is>
+      </c>
+      <c r="X21" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO2
+</t>
         </is>
       </c>
       <c r="Y21" s="1" t="inlineStr">
@@ -3962,14 +4220,18 @@
 8:31</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="AD21" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="AC21" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="AD21" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
     </row>
@@ -3984,14 +4246,18 @@
           <t>吳建昇</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="C22" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="E22" s="1" t="inlineStr">
@@ -4035,9 +4301,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="J22" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="K22" s="1" t="inlineStr">
@@ -4072,9 +4340,11 @@
 9:01</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="O22" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="P22" s="1" t="inlineStr">
@@ -4109,14 +4379,18 @@
 10:00</t>
         </is>
       </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="T22" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="U22" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="V22" s="1" t="inlineStr">
@@ -4152,14 +4426,18 @@
 9:21</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="AA22" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="Z22" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="AA22" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="AB22" s="1" t="inlineStr">
@@ -4222,14 +4500,18 @@
 8:56</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="F23" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="G23" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="H23" s="1" t="inlineStr">
@@ -4265,14 +4547,18 @@
 8:06</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="L23" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="M23" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="N23" s="1" t="inlineStr">
@@ -4307,9 +4593,11 @@
 9:11</t>
         </is>
       </c>
-      <c r="R23" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="R23" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="S23" s="1" t="inlineStr">
@@ -4344,9 +4632,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="W23" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="W23" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="X23" s="1" t="inlineStr">
@@ -4382,14 +4672,18 @@
 9:38</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="AB23" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="AC23" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="AD23" s="1" t="inlineStr">
@@ -4444,19 +4738,25 @@
 9:16</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>DO2</t>
+      <c r="G24" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="H24" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
+        </is>
+      </c>
+      <c r="I24" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO2
+</t>
         </is>
       </c>
       <c r="J24" s="1" t="inlineStr">
@@ -4499,19 +4799,25 @@
 8:00</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="O24" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="P24" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
+        </is>
+      </c>
+      <c r="Q24" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="R24" s="1" t="inlineStr">
@@ -4538,9 +4844,11 @@
 9:01</t>
         </is>
       </c>
-      <c r="U24" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="U24" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="V24" s="1" t="inlineStr">
@@ -4559,9 +4867,11 @@
 8:16</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>DO2</t>
+      <c r="X24" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO2
+</t>
         </is>
       </c>
       <c r="Y24" s="1" t="inlineStr">
@@ -4580,14 +4890,18 @@
 9:51</t>
         </is>
       </c>
-      <c r="AA24" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="AA24" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="AB24" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="AC24" s="1" t="inlineStr">
@@ -4642,14 +4956,18 @@
 8:00</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="F25" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="G25" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="H25" s="1" t="inlineStr">
@@ -4693,14 +5011,18 @@
 8:01</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="M25" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="N25" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="O25" s="1" t="inlineStr">
@@ -4735,14 +5057,18 @@
 8:11</t>
         </is>
       </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="S25" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="T25" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="U25" s="1" t="inlineStr">
@@ -4786,14 +5112,18 @@
 8:36</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="AA25" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="Z25" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="AA25" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="AB25" s="1" t="inlineStr">
@@ -4864,14 +5194,18 @@
 9:56</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="G26" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="H26" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="I26" s="1" t="inlineStr">
@@ -4899,9 +5233,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="L26" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="M26" s="1" t="inlineStr">
@@ -4928,9 +5264,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="P26" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="Q26" s="1" t="inlineStr">
@@ -4949,14 +5287,18 @@
 9:21</t>
         </is>
       </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="S26" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="T26" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="U26" s="1" t="inlineStr">
@@ -4992,9 +5334,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="Y26" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="Y26" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="Z26" s="1" t="inlineStr">
@@ -5029,9 +5373,11 @@
 9:11</t>
         </is>
       </c>
-      <c r="AD26" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="AD26" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
     </row>
@@ -5062,14 +5408,18 @@
 8:00</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="E27" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="F27" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="G27" s="1" t="inlineStr">
@@ -5105,9 +5455,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="K27" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="L27" s="1" t="inlineStr">
@@ -5126,9 +5478,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="N27" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="O27" s="1" t="inlineStr">
@@ -5155,14 +5509,18 @@
 8:00</t>
         </is>
       </c>
-      <c r="R27" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="R27" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="S27" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="T27" s="1" t="inlineStr">
@@ -5206,9 +5564,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="Y27" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="Y27" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="Z27" s="1" t="inlineStr">
@@ -5243,9 +5603,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="AD27" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="AD27" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
     </row>
@@ -5276,14 +5638,18 @@
 8:38</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="E28" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="F28" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="G28" s="1" t="inlineStr">
@@ -5311,9 +5677,11 @@
 9:56</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="J28" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="K28" s="1" t="inlineStr">
@@ -5348,9 +5716,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="O28" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="P28" s="1" t="inlineStr">
@@ -5369,9 +5739,11 @@
 8:51</t>
         </is>
       </c>
-      <c r="R28" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="R28" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="S28" s="1" t="inlineStr">
@@ -5390,9 +5762,11 @@
 9:26</t>
         </is>
       </c>
-      <c r="U28" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="U28" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="V28" s="1" t="inlineStr">
@@ -5436,9 +5810,11 @@
 9:26</t>
         </is>
       </c>
-      <c r="AA28" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="AA28" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="AB28" s="1" t="inlineStr">
@@ -5449,9 +5825,11 @@
 8:06</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="AC28" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="AD28" s="1" t="inlineStr">
@@ -5474,9 +5852,11 @@
           <t>牟君航</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="C29" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="D29" s="1" t="inlineStr">
@@ -5503,9 +5883,11 @@
 9:16</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="G29" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="H29" s="1" t="inlineStr">
@@ -5549,14 +5931,18 @@
 8:00</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="M29" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="N29" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="O29" s="1" t="inlineStr">
@@ -5599,14 +5985,18 @@
 8:01</t>
         </is>
       </c>
-      <c r="T29" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="U29" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="T29" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="U29" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="V29" s="1" t="inlineStr">
@@ -5625,14 +6015,18 @@
 8:38</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>DO2</t>
-        </is>
-      </c>
-      <c r="Y29" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="X29" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO2
+</t>
+        </is>
+      </c>
+      <c r="Y29" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="Z29" s="1" t="inlineStr">
@@ -5651,9 +6045,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="AB29" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="AC29" s="1" t="inlineStr">
@@ -5684,9 +6080,11 @@
           <t>彭權靖</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="C30" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="D30" s="1" t="inlineStr">
@@ -5721,19 +6119,25 @@
 9:46</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>DO2</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="H30" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
+        </is>
+      </c>
+      <c r="I30" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO2
+</t>
+        </is>
+      </c>
+      <c r="J30" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="K30" s="1" t="inlineStr">
@@ -5760,9 +6164,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="N30" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="O30" s="1" t="inlineStr">
@@ -5789,9 +6195,11 @@
 8:46</t>
         </is>
       </c>
-      <c r="R30" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="R30" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="S30" s="1" t="inlineStr">
@@ -5818,9 +6226,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="V30" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="V30" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="W30" s="1" t="inlineStr">
@@ -5848,9 +6258,11 @@
 9:06</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="Z30" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="AA30" s="1" t="inlineStr">
@@ -5877,9 +6289,11 @@
 9:36</t>
         </is>
       </c>
-      <c r="AD30" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="AD30" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
     </row>
@@ -5894,9 +6308,11 @@
           <t>陳椸威</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="C31" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="D31" s="1" t="inlineStr">
@@ -5923,9 +6339,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="G31" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="H31" s="1" t="inlineStr">
@@ -5936,9 +6354,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>DO2</t>
+      <c r="I31" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO2
+</t>
         </is>
       </c>
       <c r="J31" s="1" t="inlineStr">
@@ -5957,9 +6377,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="L31" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="M31" s="1" t="inlineStr">
@@ -5986,9 +6408,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="P31" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="Q31" s="1" t="inlineStr">
@@ -6007,9 +6431,11 @@
 9:16</t>
         </is>
       </c>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="S31" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="T31" s="1" t="inlineStr">
@@ -6036,14 +6462,18 @@
 8:58</t>
         </is>
       </c>
-      <c r="W31" t="inlineStr">
-        <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-      <c r="X31" t="inlineStr">
-        <is>
-          <t>DO2</t>
+      <c r="W31" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
+        </is>
+      </c>
+      <c r="X31" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO2
+</t>
         </is>
       </c>
       <c r="Y31" s="1" t="inlineStr">
@@ -6054,14 +6484,18 @@
 8:03</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="AA31" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="Z31" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="AA31" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="AB31" s="1" t="inlineStr">
@@ -6124,14 +6558,18 @@
 8:00</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="F32" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="G32" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="H32" s="1" t="inlineStr">
@@ -6167,14 +6605,18 @@
 8:00</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="L32" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="M32" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="N32" s="1" t="inlineStr">
@@ -6201,9 +6643,11 @@
 9:56</t>
         </is>
       </c>
-      <c r="Q32" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="Q32" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="R32" s="1" t="inlineStr">
@@ -6230,9 +6674,11 @@
 8:56</t>
         </is>
       </c>
-      <c r="U32" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="U32" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="V32" s="1" t="inlineStr">
@@ -6276,14 +6722,18 @@
 9:01</t>
         </is>
       </c>
-      <c r="AA32" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="AA32" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="AB32" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="AC32" s="1" t="inlineStr">
@@ -6330,14 +6780,18 @@
 8:00</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="E33" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="F33" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="G33" s="1" t="inlineStr">
@@ -6356,9 +6810,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>DO2</t>
+      <c r="I33" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO2
+</t>
         </is>
       </c>
       <c r="J33" s="1" t="inlineStr">
@@ -6369,9 +6825,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="K33" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="L33" s="1" t="inlineStr">
@@ -6398,9 +6856,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="O33" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="P33" s="1" t="inlineStr">
@@ -6435,14 +6895,18 @@
 8:00</t>
         </is>
       </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="T33" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="U33" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="V33" s="1" t="inlineStr">
@@ -6478,9 +6942,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="Z33" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="AA33" s="1" t="inlineStr">
@@ -6507,9 +6973,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="AD33" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="AD33" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
     </row>
@@ -6548,14 +7016,18 @@
 8:00</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="F34" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="G34" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="H34" s="1" t="inlineStr">
@@ -6566,9 +7038,11 @@
 9:16</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>DO2</t>
+      <c r="I34" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO2
+</t>
         </is>
       </c>
       <c r="J34" s="1" t="inlineStr">
@@ -6595,9 +7069,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="M34" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="N34" s="1" t="inlineStr">
@@ -6616,9 +7092,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="P34" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="Q34" s="1" t="inlineStr">
@@ -6629,9 +7107,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="R34" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="R34" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="S34" s="1" t="inlineStr">
@@ -6650,9 +7130,11 @@
 8:01</t>
         </is>
       </c>
-      <c r="U34" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="U34" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="V34" s="1" t="inlineStr">
@@ -6688,14 +7170,18 @@
 8:00</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="AA34" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="Z34" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="AA34" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="AB34" s="1" t="inlineStr">
@@ -6742,14 +7228,18 @@
 8:00</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="D35" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="E35" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="F35" s="1" t="inlineStr">
@@ -6776,14 +7266,18 @@
 8:00</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>DO2</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="I35" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO2
+</t>
+        </is>
+      </c>
+      <c r="J35" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="K35" s="1" t="inlineStr">
@@ -6802,9 +7296,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="M35" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="N35" s="1" t="inlineStr">
@@ -6855,9 +7351,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="T35" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="U35" s="1" t="inlineStr">
@@ -6868,9 +7366,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="V35" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="W35" s="1" t="inlineStr">
@@ -6922,14 +7422,18 @@
 9:26</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="AD35" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="AC35" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="AD35" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
     </row>
@@ -6960,9 +7464,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="E36" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="F36" s="1" t="inlineStr">
@@ -6981,19 +7487,25 @@
 8:00</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>DO2</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="H36" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
+        </is>
+      </c>
+      <c r="I36" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO2
+</t>
+        </is>
+      </c>
+      <c r="J36" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="K36" s="1" t="inlineStr">
@@ -7036,9 +7548,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="P36" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="Q36" s="1" t="inlineStr">
@@ -7065,14 +7579,18 @@
 8:00</t>
         </is>
       </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="T36" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="U36" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="V36" s="1" t="inlineStr">
@@ -7116,14 +7634,18 @@
 8:00</t>
         </is>
       </c>
-      <c r="AA36" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="AA36" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="AB36" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="AC36" s="1" t="inlineStr">
@@ -7178,14 +7700,18 @@
 9:51</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="F37" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="G37" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="H37" s="1" t="inlineStr">
@@ -7213,9 +7739,11 @@
 8:16</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="K37" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="L37" s="1" t="inlineStr">
@@ -7250,9 +7778,11 @@
 9:00</t>
         </is>
       </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="P37" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="Q37" s="1" t="inlineStr">
@@ -7295,19 +7825,25 @@
 8:00</t>
         </is>
       </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>DO2</t>
+      <c r="V37" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="W37" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
+        </is>
+      </c>
+      <c r="X37" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO2
+</t>
         </is>
       </c>
       <c r="Y37" s="1" t="inlineStr">
@@ -7342,14 +7878,18 @@
 8:00</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="AD37" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="AC37" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="AD37" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
     </row>
@@ -7372,14 +7912,18 @@
 8:00</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="D38" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="E38" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="F38" s="1" t="inlineStr">
@@ -7406,14 +7950,18 @@
 8:00</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>DO2</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="I38" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO2
+</t>
+        </is>
+      </c>
+      <c r="J38" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="K38" s="1" t="inlineStr">
@@ -7432,9 +7980,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="M38" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="N38" s="1" t="inlineStr">
@@ -7477,9 +8027,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="S38" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="S38" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="T38" s="1" t="inlineStr">
@@ -7506,24 +8058,32 @@
 8:00</t>
         </is>
       </c>
-      <c r="W38" t="inlineStr">
-        <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-      <c r="X38" t="inlineStr">
-        <is>
-          <t>DO2</t>
-        </is>
-      </c>
-      <c r="Y38" t="inlineStr">
-        <is>
-          <t>DO2</t>
-        </is>
-      </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="W38" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
+        </is>
+      </c>
+      <c r="X38" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO2
+</t>
+        </is>
+      </c>
+      <c r="Y38" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO2
+</t>
+        </is>
+      </c>
+      <c r="Z38" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="AA38" s="1" t="inlineStr">
@@ -7550,9 +8110,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="AD38" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="AD38" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
     </row>
@@ -7583,9 +8145,11 @@
 8:11</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="E39" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="F39" s="1" t="inlineStr">
@@ -7596,9 +8160,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="G39" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="H39" s="1" t="inlineStr">
@@ -7609,9 +8175,11 @@
 8:56</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>DO2</t>
+      <c r="I39" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO2
+</t>
         </is>
       </c>
       <c r="J39" s="1" t="inlineStr">
@@ -7646,14 +8214,18 @@
 8:00</t>
         </is>
       </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="O39" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="N39" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="O39" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="P39" s="1" t="inlineStr">
@@ -7680,9 +8252,11 @@
 8:16</t>
         </is>
       </c>
-      <c r="S39" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="S39" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="T39" s="1" t="inlineStr">
@@ -7709,9 +8283,11 @@
 8:16</t>
         </is>
       </c>
-      <c r="W39" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="W39" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="X39" s="1" t="inlineStr">
@@ -7731,9 +8307,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="Z39" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="AA39" s="1" t="inlineStr">
@@ -7744,9 +8322,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="AB39" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="AC39" s="1" t="inlineStr">
@@ -7793,14 +8373,18 @@
 9:51</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="E40" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="F40" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="G40" s="1" t="inlineStr">
@@ -7844,14 +8428,18 @@
 9:51</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="L40" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="M40" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="N40" s="1" t="inlineStr">
@@ -7878,9 +8466,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="Q40" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="Q40" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="R40" s="1" t="inlineStr">
@@ -7923,9 +8513,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="W40" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="W40" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="X40" s="1" t="inlineStr">
@@ -7961,14 +8553,18 @@
 8:00</t>
         </is>
       </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="AB40" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="AC40" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="AD40" s="1" t="inlineStr">
@@ -7999,14 +8595,18 @@
 9:36</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="D41" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="E41" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="F41" s="1" t="inlineStr">
@@ -8058,14 +8658,18 @@
 8:16</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="L41" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="M41" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="N41" s="1" t="inlineStr">
@@ -8108,14 +8712,18 @@
 8:00</t>
         </is>
       </c>
-      <c r="S41" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="T41" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="S41" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="T41" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="U41" s="1" t="inlineStr">
@@ -8159,9 +8767,11 @@
 9:51</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="Z41" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="AA41" s="1" t="inlineStr">
@@ -8188,9 +8798,11 @@
 9:31</t>
         </is>
       </c>
-      <c r="AD41" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="AD41" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
     </row>
@@ -8221,14 +8833,18 @@
 8:41</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="E42" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="F42" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="G42" s="1" t="inlineStr">
@@ -8264,9 +8880,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="K42" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="L42" s="1" t="inlineStr">
@@ -8301,14 +8919,18 @@
 8:37</t>
         </is>
       </c>
-      <c r="P42" t="inlineStr">
-        <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-      <c r="Q42" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="P42" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
+        </is>
+      </c>
+      <c r="Q42" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="R42" s="1" t="inlineStr">
@@ -8351,14 +8973,18 @@
 8:00</t>
         </is>
       </c>
-      <c r="W42" t="inlineStr">
-        <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-      <c r="X42" t="inlineStr">
-        <is>
-          <t>DO2</t>
+      <c r="W42" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
+        </is>
+      </c>
+      <c r="X42" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO2
+</t>
         </is>
       </c>
       <c r="Y42" s="1" t="inlineStr">
@@ -8385,14 +9011,18 @@
 10:00</t>
         </is>
       </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="AB42" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="AC42" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="AD42" s="1" t="inlineStr">
@@ -8431,14 +9061,18 @@
 8:00</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="E43" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="F43" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="G43" s="1" t="inlineStr">
@@ -8482,14 +9116,18 @@
 8:00</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="L43" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="M43" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="N43" s="1" t="inlineStr">
@@ -8516,9 +9154,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="Q43" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="Q43" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="R43" s="1" t="inlineStr">
@@ -8545,9 +9185,11 @@
 8:41</t>
         </is>
       </c>
-      <c r="U43" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="U43" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="V43" s="1" t="inlineStr">
@@ -8566,14 +9208,18 @@
 8:00</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr">
-        <is>
-          <t>DO2</t>
-        </is>
-      </c>
-      <c r="Y43" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="X43" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO2
+</t>
+        </is>
+      </c>
+      <c r="Y43" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="Z43" s="1" t="inlineStr">
@@ -8600,9 +9246,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="AC43" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="AD43" s="1" t="inlineStr">
@@ -8641,14 +9289,18 @@
 8:00</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="E44" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="F44" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="G44" s="1" t="inlineStr">
@@ -8667,9 +9319,11 @@
 10:00</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>DO2</t>
+      <c r="I44" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO2
+</t>
         </is>
       </c>
       <c r="J44" s="1" t="inlineStr">
@@ -8680,9 +9334,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="K44" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="L44" s="1" t="inlineStr">
@@ -8709,9 +9365,11 @@
 9:11</t>
         </is>
       </c>
-      <c r="O44" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="O44" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="P44" s="1" t="inlineStr">
@@ -8730,9 +9388,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="R44" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="R44" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="S44" s="1" t="inlineStr">
@@ -8751,9 +9411,11 @@
 8:28</t>
         </is>
       </c>
-      <c r="U44" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="U44" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="V44" s="1" t="inlineStr">
@@ -8772,9 +9434,11 @@
 9:20</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr">
-        <is>
-          <t>DO2</t>
+      <c r="X44" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO2
+</t>
         </is>
       </c>
       <c r="Y44" s="1" t="inlineStr">
@@ -8793,14 +9457,18 @@
 8:00</t>
         </is>
       </c>
-      <c r="AA44" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="AA44" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="AB44" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="AC44" s="1" t="inlineStr">
@@ -8831,9 +9499,11 @@
           <t>江杰叡</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="C45" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="D45" s="1" t="inlineStr">
@@ -8852,9 +9522,11 @@
 9:01</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="F45" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="G45" s="1" t="inlineStr">
@@ -8890,14 +9562,18 @@
 9:30</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="K45" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="L45" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="M45" s="1" t="inlineStr">
@@ -8940,9 +9616,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="R45" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="R45" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="S45" s="1" t="inlineStr">
@@ -8969,9 +9647,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="V45" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="V45" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="W45" s="1" t="inlineStr">
@@ -9015,14 +9695,18 @@
 9:26</t>
         </is>
       </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="AB45" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="AC45" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="AD45" s="1" t="inlineStr">
@@ -9045,14 +9729,18 @@
           <t>吳睿哲</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="C46" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="D46" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="E46" s="1" t="inlineStr">
@@ -9096,9 +9784,11 @@
 9:26</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="J46" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="K46" s="1" t="inlineStr">
@@ -9141,14 +9831,18 @@
 8:26</t>
         </is>
       </c>
-      <c r="P46" t="inlineStr">
-        <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-      <c r="Q46" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="P46" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
+        </is>
+      </c>
+      <c r="Q46" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="R46" s="1" t="inlineStr">
@@ -9191,19 +9885,25 @@
 8:00</t>
         </is>
       </c>
-      <c r="W46" t="inlineStr">
-        <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-      <c r="X46" t="inlineStr">
-        <is>
-          <t>DO2</t>
-        </is>
-      </c>
-      <c r="Y46" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="W46" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
+        </is>
+      </c>
+      <c r="X46" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO2
+</t>
+        </is>
+      </c>
+      <c r="Y46" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="Z46" s="1" t="inlineStr">
@@ -9238,9 +9938,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="AD46" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="AD46" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
     </row>
@@ -9255,9 +9957,11 @@
           <t>吳子昌</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="C47" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="D47" s="1" t="inlineStr">
@@ -9292,9 +9996,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="H47" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="I47" s="1" t="inlineStr">
@@ -9306,14 +10012,18 @@
 9:01</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="J47" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="K47" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="L47" s="1" t="inlineStr">
@@ -9364,14 +10074,18 @@
 9:21</t>
         </is>
       </c>
-      <c r="R47" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="S47" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="R47" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="S47" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="T47" s="1" t="inlineStr">
@@ -9415,9 +10129,11 @@
 8:11</t>
         </is>
       </c>
-      <c r="Y47" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="Y47" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="Z47" s="1" t="inlineStr">
@@ -9452,9 +10168,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="AD47" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="AD47" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
     </row>
@@ -9469,9 +10187,11 @@
           <t>江之聖</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="C48" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="D48" s="1" t="inlineStr">
@@ -9506,9 +10226,11 @@
 9:01</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="H48" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="I48" s="1" t="inlineStr">
@@ -9536,14 +10258,18 @@
 9:30</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="L48" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="M48" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="N48" s="1" t="inlineStr">
@@ -9578,9 +10304,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="R48" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="R48" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="S48" s="1" t="inlineStr">
@@ -9607,9 +10335,11 @@
 8:06</t>
         </is>
       </c>
-      <c r="V48" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="V48" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="W48" s="1" t="inlineStr">
@@ -9637,14 +10367,18 @@
 8:00</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="AA48" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="Z48" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="AA48" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="AB48" s="1" t="inlineStr">
@@ -9691,14 +10425,18 @@
 9:41</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="D49" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="E49" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="F49" s="1" t="inlineStr">
@@ -9725,9 +10463,11 @@
 9:06</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>DO2</t>
+      <c r="I49" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO2
+</t>
         </is>
       </c>
       <c r="J49" s="1" t="inlineStr">
@@ -9746,14 +10486,18 @@
 9:26</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="L49" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="M49" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="N49" s="1" t="inlineStr">
@@ -9796,9 +10540,11 @@
 8:06</t>
         </is>
       </c>
-      <c r="S49" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="S49" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="T49" s="1" t="inlineStr">
@@ -9817,9 +10563,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="V49" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="V49" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="W49" s="1" t="inlineStr">
@@ -9854,14 +10602,18 @@
 9:38</t>
         </is>
       </c>
-      <c r="AA49" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="AA49" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="AB49" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="AC49" s="1" t="inlineStr">
@@ -9900,14 +10652,18 @@
 10:00</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="D50" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="E50" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="F50" s="1" t="inlineStr">
@@ -9951,9 +10707,11 @@
 8:41</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="K50" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="L50" s="1" t="inlineStr">
@@ -9988,9 +10746,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="P50" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="P50" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="Q50" s="1" t="inlineStr">
@@ -10033,24 +10793,32 @@
 8:00</t>
         </is>
       </c>
-      <c r="V50" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="W50" t="inlineStr">
-        <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-      <c r="X50" t="inlineStr">
-        <is>
-          <t>DO2</t>
-        </is>
-      </c>
-      <c r="Y50" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="V50" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="W50" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
+        </is>
+      </c>
+      <c r="X50" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO2
+</t>
+        </is>
+      </c>
+      <c r="Y50" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="Z50" s="1" t="inlineStr">
@@ -10085,9 +10853,11 @@
 8:26</t>
         </is>
       </c>
-      <c r="AD50" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="AD50" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
     </row>
@@ -10126,14 +10896,18 @@
 8:16</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="F51" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="G51" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="H51" s="1" t="inlineStr">
@@ -10161,9 +10935,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="K51" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="L51" s="1" t="inlineStr">
@@ -10198,19 +10974,25 @@
 8:01</t>
         </is>
       </c>
-      <c r="P51" t="inlineStr">
-        <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-      <c r="Q51" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="R51" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="P51" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
+        </is>
+      </c>
+      <c r="Q51" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="R51" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="S51" s="1" t="inlineStr">
@@ -10253,14 +11035,18 @@
 8:36</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr">
-        <is>
-          <t>DO2</t>
-        </is>
-      </c>
-      <c r="Y51" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="X51" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO2
+</t>
+        </is>
+      </c>
+      <c r="Y51" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="Z51" s="1" t="inlineStr">
@@ -10295,9 +11081,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="AD51" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="AD51" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
     </row>
@@ -10336,9 +11124,11 @@
 8:46</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="F52" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="G52" s="1" t="inlineStr">
@@ -10349,14 +11139,18 @@
 8:00</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>DO2</t>
+      <c r="H52" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
+        </is>
+      </c>
+      <c r="I52" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO2
+</t>
         </is>
       </c>
       <c r="J52" s="1" t="inlineStr">
@@ -10383,14 +11177,18 @@
 9:26</t>
         </is>
       </c>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="M52" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="N52" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="O52" s="1" t="inlineStr">
@@ -10433,9 +11231,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="T52" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="T52" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="U52" s="1" t="inlineStr">
@@ -10454,9 +11254,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="W52" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="W52" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="X52" s="1" t="inlineStr">
@@ -10476,14 +11278,18 @@
 8:06</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="AA52" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="Z52" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="AA52" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="AB52" s="1" t="inlineStr">
@@ -10530,14 +11336,18 @@
 8:00</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="D53" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="E53" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="F53" s="1" t="inlineStr">
@@ -10581,9 +11391,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="K53" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="L53" s="1" t="inlineStr">
@@ -10610,9 +11422,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="O53" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="O53" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="P53" s="1" t="inlineStr">
@@ -10639,9 +11453,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="S53" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="S53" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="T53" s="1" t="inlineStr">
@@ -10668,9 +11484,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="W53" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="W53" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="X53" s="1" t="inlineStr">
@@ -10706,14 +11524,18 @@
 8:00</t>
         </is>
       </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="AB53" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="AC53" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="AD53" s="1" t="inlineStr">
@@ -10744,14 +11566,18 @@
 8:00</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="D54" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="E54" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="F54" s="1" t="inlineStr">
@@ -10795,9 +11621,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="K54" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="L54" s="1" t="inlineStr">
@@ -10832,9 +11660,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="P54" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="P54" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="Q54" s="1" t="inlineStr">
@@ -10853,14 +11683,18 @@
 8:41</t>
         </is>
       </c>
-      <c r="S54" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="T54" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="S54" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="T54" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="U54" s="1" t="inlineStr">
@@ -10887,9 +11721,11 @@
 8:31</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr">
-        <is>
-          <t>DO2</t>
+      <c r="X54" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO2
+</t>
         </is>
       </c>
       <c r="Y54" s="1" t="inlineStr">
@@ -10908,14 +11744,18 @@
 8:00</t>
         </is>
       </c>
-      <c r="AA54" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="AA54" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="AB54" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="AC54" s="1" t="inlineStr">
@@ -10962,14 +11802,18 @@
 8:00</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="E55" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="F55" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="G55" s="1" t="inlineStr">
@@ -10997,9 +11841,11 @@
 9:11</t>
         </is>
       </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="J55" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="K55" s="1" t="inlineStr">
@@ -11042,9 +11888,11 @@
 8:16</t>
         </is>
       </c>
-      <c r="P55" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="P55" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="Q55" s="1" t="inlineStr">
@@ -11055,9 +11903,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="R55" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="R55" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="S55" s="1" t="inlineStr">
@@ -11084,9 +11934,11 @@
 8:31</t>
         </is>
       </c>
-      <c r="V55" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="V55" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="W55" s="1" t="inlineStr">
@@ -11130,14 +11982,18 @@
 9:01</t>
         </is>
       </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="AB55" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="AC55" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="AD55" s="1" t="inlineStr">
@@ -11168,14 +12024,18 @@
 9:26</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="D56" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="E56" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="F56" s="1" t="inlineStr">
@@ -11219,9 +12079,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="K56" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="L56" s="1" t="inlineStr">
@@ -11256,19 +12118,25 @@
 8:46</t>
         </is>
       </c>
-      <c r="P56" t="inlineStr">
-        <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-      <c r="Q56" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="R56" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="P56" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
+        </is>
+      </c>
+      <c r="Q56" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="R56" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="S56" s="1" t="inlineStr">
@@ -11320,14 +12188,18 @@
 9:36</t>
         </is>
       </c>
-      <c r="Y56" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="Y56" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="Z56" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="AA56" s="1" t="inlineStr">
@@ -11382,14 +12254,18 @@
 8:00</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="D57" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="E57" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="F57" s="1" t="inlineStr">
@@ -11433,9 +12309,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="K57" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="L57" s="1" t="inlineStr">
@@ -11446,9 +12324,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="M57" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="N57" s="1" t="inlineStr">
@@ -11483,9 +12363,11 @@
 8:16</t>
         </is>
       </c>
-      <c r="R57" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="R57" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="S57" s="1" t="inlineStr">
@@ -11520,9 +12402,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="W57" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="W57" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="X57" s="1" t="inlineStr">
@@ -11558,14 +12442,18 @@
 9:21</t>
         </is>
       </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="AB57" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="AC57" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="AD57" s="1" t="inlineStr">
@@ -11604,14 +12492,18 @@
 8:06</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="E58" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="F58" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="G58" s="1" t="inlineStr">
@@ -11655,9 +12547,11 @@
 8:46</t>
         </is>
       </c>
-      <c r="L58" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="L58" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="M58" s="1" t="inlineStr">
@@ -11684,14 +12578,18 @@
 8:00</t>
         </is>
       </c>
-      <c r="P58" t="inlineStr">
-        <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-      <c r="Q58" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="P58" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
+        </is>
+      </c>
+      <c r="Q58" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="R58" s="1" t="inlineStr">
@@ -11718,9 +12616,11 @@
 9:56</t>
         </is>
       </c>
-      <c r="U58" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="U58" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="V58" s="1" t="inlineStr">
@@ -11739,9 +12639,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>DO2</t>
+      <c r="X58" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO2
+</t>
         </is>
       </c>
       <c r="Y58" s="1" t="inlineStr">
@@ -11752,14 +12654,18 @@
 8:16</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="AA58" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="Z58" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="AA58" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="AB58" s="1" t="inlineStr">
@@ -11798,9 +12704,11 @@
           <t>留煒翔</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="C59" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="D59" s="1" t="inlineStr">
@@ -11835,9 +12743,11 @@
 9:41</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="H59" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="I59" s="1" t="inlineStr">
@@ -11849,9 +12759,11 @@
 8:31</t>
         </is>
       </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="J59" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="K59" s="1" t="inlineStr">
@@ -11894,9 +12806,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="P59" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="P59" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="Q59" s="1" t="inlineStr">
@@ -11923,14 +12837,18 @@
 9:16</t>
         </is>
       </c>
-      <c r="T59" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="U59" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="T59" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="U59" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="V59" s="1" t="inlineStr">
@@ -11966,14 +12884,18 @@
 8:00</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="AA59" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="Z59" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="AA59" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="AB59" s="1" t="inlineStr">
@@ -12020,9 +12942,11 @@
 9:11</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="D60" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="E60" s="1" t="inlineStr">
@@ -12049,14 +12973,18 @@
 8:41</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>DO2</t>
+      <c r="H60" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
+        </is>
+      </c>
+      <c r="I60" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO2
+</t>
         </is>
       </c>
       <c r="J60" s="1" t="inlineStr">
@@ -12083,14 +13011,18 @@
 8:00</t>
         </is>
       </c>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="M60" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="N60" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="O60" s="1" t="inlineStr">
@@ -12125,9 +13057,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="S60" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="S60" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="T60" s="1" t="inlineStr">
@@ -12154,9 +13088,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="W60" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="W60" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="X60" s="1" t="inlineStr">
@@ -12200,14 +13136,18 @@
 8:00</t>
         </is>
       </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="AD60" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="AC60" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="AD60" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
     </row>
@@ -12230,14 +13170,18 @@
 8:16</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="D61" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="E61" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="F61" s="1" t="inlineStr">
@@ -12281,9 +13225,11 @@
 8:06</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="K61" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="L61" s="1" t="inlineStr">
@@ -12318,9 +13264,11 @@
 9:45</t>
         </is>
       </c>
-      <c r="P61" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="P61" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="Q61" s="1" t="inlineStr">
@@ -12363,24 +13311,32 @@
 8:00</t>
         </is>
       </c>
-      <c r="V61" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="W61" t="inlineStr">
-        <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-      <c r="X61" t="inlineStr">
-        <is>
-          <t>DO2</t>
-        </is>
-      </c>
-      <c r="Y61" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="V61" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="W61" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
+        </is>
+      </c>
+      <c r="X61" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO2
+</t>
+        </is>
+      </c>
+      <c r="Y61" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="Z61" s="1" t="inlineStr">
@@ -12407,9 +13363,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="AC61" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="AD61" s="1" t="inlineStr">
@@ -12432,14 +13390,18 @@
           <t>李俊賢</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="C62" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="D62" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="E62" s="1" t="inlineStr">
@@ -12491,9 +13453,11 @@
 9:21</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="K62" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="L62" s="1" t="inlineStr">
@@ -12520,9 +13484,11 @@
 9:21</t>
         </is>
       </c>
-      <c r="O62" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="O62" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="P62" s="1" t="inlineStr">
@@ -12549,14 +13515,18 @@
 8:00</t>
         </is>
       </c>
-      <c r="S62" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="T62" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="S62" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="T62" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="U62" s="1" t="inlineStr">
@@ -12600,14 +13570,18 @@
 10:00</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="AA62" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="Z62" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="AA62" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="AB62" s="1" t="inlineStr">
@@ -12670,9 +13644,11 @@
 8:41</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="F63" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="G63" s="1" t="inlineStr">
@@ -12725,14 +13701,18 @@
 8:00</t>
         </is>
       </c>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="M63" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="N63" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="O63" s="1" t="inlineStr">
@@ -12767,14 +13747,18 @@
 8:31</t>
         </is>
       </c>
-      <c r="S63" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="T63" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="S63" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="T63" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="U63" s="1" t="inlineStr">
@@ -12826,9 +13810,11 @@
 9:36</t>
         </is>
       </c>
-      <c r="AA63" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="AA63" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="AB63" s="1" t="inlineStr">
@@ -12847,9 +13833,11 @@
 8:37</t>
         </is>
       </c>
-      <c r="AD63" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="AD63" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
     </row>
@@ -12872,14 +13860,18 @@
 8:06</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="D64" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="E64" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="F64" s="1" t="inlineStr">
@@ -12906,9 +13898,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>DO2</t>
+      <c r="I64" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO2
+</t>
         </is>
       </c>
       <c r="J64" s="1" t="inlineStr">
@@ -12919,9 +13913,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="K64" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="L64" s="1" t="inlineStr">
@@ -12948,9 +13944,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="O64" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="O64" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="P64" s="1" t="inlineStr">
@@ -12985,14 +13983,18 @@
 9:16</t>
         </is>
       </c>
-      <c r="T64" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="U64" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="T64" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="U64" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="V64" s="1" t="inlineStr">
@@ -13020,9 +14022,11 @@
 8:16</t>
         </is>
       </c>
-      <c r="Y64" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="Y64" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="Z64" s="1" t="inlineStr">
@@ -13041,9 +14045,11 @@
 9:51</t>
         </is>
       </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="AB64" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="AC64" s="1" t="inlineStr">
